--- a/Results/Comparison.xlsx
+++ b/Results/Comparison.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nikoo\Desktop\Thesis\Source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69BC2A2E-CCBF-486C-B7A9-5536D2ED42C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94857F76-471F-42AA-84BD-98EE4C7B8BBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{8D592C9F-CC51-43DD-B2E3-0BF015735963}"/>
   </bookViews>
@@ -332,7 +332,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -340,22 +340,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -369,21 +360,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -442,15 +418,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -841,31 +808,31 @@
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D2">
-        <v>0.55982834994462805</v>
+        <v>0.72452431289640495</v>
       </c>
       <c r="E2">
-        <v>0.223338830964533</v>
+        <v>0.12634112205655601</v>
       </c>
       <c r="F2">
-        <v>0.61168327796234701</v>
+        <v>0.70793418467836999</v>
       </c>
       <c r="G2">
-        <v>0.21813197205084001</v>
+        <v>0.14239179692925599</v>
       </c>
       <c r="H2">
-        <v>0.58449612403100704</v>
+        <v>0.65808416389811697</v>
       </c>
       <c r="I2">
-        <v>0.241453269825704</v>
+        <v>0.17755312426902001</v>
       </c>
       <c r="J2">
-        <v>0.71124031007751898</v>
+        <v>0.819961240310077</v>
       </c>
       <c r="K2">
-        <v>0.294407848079422</v>
+        <v>0.17530527934034201</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
@@ -876,31 +843,31 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D3">
-        <v>0.51915836101882595</v>
+        <v>0.61860465116278995</v>
       </c>
       <c r="E3">
-        <v>0.21005667760602001</v>
+        <v>0.147057152906341</v>
       </c>
       <c r="F3">
-        <v>0.57753783684016202</v>
+        <v>0.48659854357528698</v>
       </c>
       <c r="G3">
-        <v>0.21822987449706099</v>
+        <v>0.23057853355097499</v>
       </c>
       <c r="H3">
-        <v>0.53139534883720896</v>
+        <v>0.57314507198228104</v>
       </c>
       <c r="I3">
-        <v>0.22114364777208201</v>
+        <v>0.28022744816873202</v>
       </c>
       <c r="J3">
-        <v>0.68604651162790697</v>
+        <v>0.49025470653377601</v>
       </c>
       <c r="K3">
-        <v>0.28970113425852101</v>
+        <v>0.28321899195455902</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
@@ -911,31 +878,31 @@
         <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D4">
-        <v>0.54587486157253595</v>
+        <v>0.54186046511627906</v>
       </c>
       <c r="E4">
-        <v>0.22100281005625499</v>
+        <v>0.13878941103190401</v>
       </c>
       <c r="F4">
-        <v>0.56987818383167199</v>
+        <v>0.40919700454584101</v>
       </c>
       <c r="G4">
-        <v>0.255186088588988</v>
+        <v>0.19444552422140901</v>
       </c>
       <c r="H4">
-        <v>0.54186046511627906</v>
+        <v>0.45802879291251303</v>
       </c>
       <c r="I4">
-        <v>0.25554249162544401</v>
+        <v>0.236613898616195</v>
       </c>
       <c r="J4">
-        <v>0.64534883720930203</v>
+        <v>0.41694352159468401</v>
       </c>
       <c r="K4">
-        <v>0.31749840955461001</v>
+        <v>0.22895421142504299</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
@@ -946,31 +913,31 @@
         <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D5">
-        <v>0.47724252491694302</v>
+        <v>0.52748414376321295</v>
       </c>
       <c r="E5">
-        <v>0.23198943013223999</v>
+        <v>0.14176732936727399</v>
       </c>
       <c r="F5">
-        <v>0.56831605087419002</v>
+        <v>0.376273080924243</v>
       </c>
       <c r="G5">
-        <v>0.253344863016497</v>
+        <v>0.23752310296649501</v>
       </c>
       <c r="H5">
-        <v>0.48576965669988897</v>
+        <v>0.42054263565891398</v>
       </c>
       <c r="I5">
-        <v>0.245817992341653</v>
+        <v>0.26718885416195898</v>
       </c>
       <c r="J5">
-        <v>0.74806201550387597</v>
+        <v>0.38410852713178201</v>
       </c>
       <c r="K5">
-        <v>0.34686132918472301</v>
+        <v>0.28085462990170401</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
@@ -984,28 +951,28 @@
         <v>12</v>
       </c>
       <c r="D6">
-        <v>0.52414174972314498</v>
+        <v>0.70993657505285401</v>
       </c>
       <c r="E6">
-        <v>0.221110454751174</v>
+        <v>0.12249902749579</v>
       </c>
       <c r="F6">
-        <v>0.60844155844155801</v>
+        <v>0.69342853528899995</v>
       </c>
       <c r="G6">
-        <v>0.25327050959811298</v>
+        <v>0.13723894892184399</v>
       </c>
       <c r="H6">
-        <v>0.505537098560354</v>
+        <v>0.650913621262458</v>
       </c>
       <c r="I6">
-        <v>0.23207887122842899</v>
+        <v>0.18556441073274901</v>
       </c>
       <c r="J6">
-        <v>0.80426356589147197</v>
+        <v>0.805841638981173</v>
       </c>
       <c r="K6">
-        <v>0.32937755531285601</v>
+        <v>0.18342370490437901</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
@@ -1016,31 +983,31 @@
         <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D7">
-        <v>0.52187153931339902</v>
+        <v>0.56680761099365695</v>
       </c>
       <c r="E7">
-        <v>0.21973282006032399</v>
+        <v>0.13022672346282799</v>
       </c>
       <c r="F7">
-        <v>0.59307862679955703</v>
+        <v>0.39594346222253202</v>
       </c>
       <c r="G7">
-        <v>0.233962366537284</v>
+        <v>0.238376007132796</v>
       </c>
       <c r="H7">
-        <v>0.52209302325581397</v>
+        <v>0.441786637135474</v>
       </c>
       <c r="I7">
-        <v>0.23923113628102799</v>
+        <v>0.30926351009386199</v>
       </c>
       <c r="J7">
-        <v>0.74031007751937905</v>
+        <v>0.42093023255813899</v>
       </c>
       <c r="K7">
-        <v>0.30931349671885999</v>
+        <v>0.28549020288911198</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
@@ -1051,31 +1018,31 @@
         <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D8">
-        <v>0.49202657807308903</v>
+        <v>0.51395348837209298</v>
       </c>
       <c r="E8">
-        <v>0.223799441186221</v>
+        <v>0.130381082765363</v>
       </c>
       <c r="F8">
-        <v>0.53864894795127305</v>
+        <v>0.34942680058959102</v>
       </c>
       <c r="G8">
-        <v>0.24973372794964399</v>
+        <v>0.232072836102137</v>
       </c>
       <c r="H8">
-        <v>0.49457364341085203</v>
+        <v>0.38103543743078599</v>
       </c>
       <c r="I8">
-        <v>0.25321501036840699</v>
+        <v>0.276812031560489</v>
       </c>
       <c r="J8">
-        <v>0.63953488372093004</v>
+        <v>0.361240310077519</v>
       </c>
       <c r="K8">
-        <v>0.32929772694200599</v>
+        <v>0.24117735218907199</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
@@ -1086,31 +1053,31 @@
         <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D9">
-        <v>0.52837763012181604</v>
+        <v>0.49450317124735699</v>
       </c>
       <c r="E9">
-        <v>0.25103092955919498</v>
+        <v>0.10854584647769699</v>
       </c>
       <c r="F9">
-        <v>0.53204134366925004</v>
+        <v>0.33839493839493801</v>
       </c>
       <c r="G9">
-        <v>0.31522208497998599</v>
+        <v>0.17867296269323699</v>
       </c>
       <c r="H9">
-        <v>0.48139534883720903</v>
+        <v>0.37353266888150599</v>
       </c>
       <c r="I9">
-        <v>0.29901235579643698</v>
+        <v>0.20606682582033001</v>
       </c>
       <c r="J9">
-        <v>0.62209302325581395</v>
+        <v>0.35559246954595702</v>
       </c>
       <c r="K9">
-        <v>0.37239571021976697</v>
+        <v>0.22738182713701699</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
@@ -1124,28 +1091,28 @@
         <v>12</v>
       </c>
       <c r="D10">
-        <v>0.57078290370370899</v>
+        <v>0.85476754021099299</v>
       </c>
       <c r="E10">
-        <v>0.15490427070801899</v>
+        <v>0.164461385373316</v>
       </c>
       <c r="F10">
-        <v>0.71087331052276703</v>
+        <v>0.80936807219704598</v>
       </c>
       <c r="G10">
-        <v>0.126091914079447</v>
+        <v>0.20241393067035701</v>
       </c>
       <c r="H10">
-        <v>0.57285731667172102</v>
+        <v>0.86613726602382302</v>
       </c>
       <c r="I10">
-        <v>0.155324348395141</v>
+        <v>0.21913846302265</v>
       </c>
       <c r="J10">
-        <v>0.978653299484598</v>
+        <v>0.78970169273031898</v>
       </c>
       <c r="K10">
-        <v>7.5921446275818399E-2</v>
+        <v>0.228405686826789</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
@@ -1156,31 +1123,31 @@
         <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D11">
-        <v>0.54148473300758104</v>
+        <v>0.62151622960802899</v>
       </c>
       <c r="E11">
-        <v>0.103399686348495</v>
+        <v>0.13468267500880399</v>
       </c>
       <c r="F11">
-        <v>0.64745766574953001</v>
+        <v>0.49043386633550401</v>
       </c>
       <c r="G11">
-        <v>0.115909381967172</v>
+        <v>0.17615792337158401</v>
       </c>
       <c r="H11">
-        <v>0.57441812991147301</v>
+        <v>0.54753001969928705</v>
       </c>
       <c r="I11">
-        <v>0.15313347451566001</v>
+        <v>0.22074265292426901</v>
       </c>
       <c r="J11">
-        <v>0.78774340837664303</v>
+        <v>0.52735964681776903</v>
       </c>
       <c r="K11">
-        <v>0.14726940353002399</v>
+        <v>0.26838495731504902</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
@@ -1194,28 +1161,28 @@
         <v>14</v>
       </c>
       <c r="D12">
-        <v>0.50584145565761196</v>
+        <v>0.52850216899770497</v>
       </c>
       <c r="E12">
-        <v>7.3341889751700196E-2</v>
+        <v>5.83606083461716E-2</v>
       </c>
       <c r="F12">
-        <v>0.58444461268909798</v>
+        <v>0.37508689676345702</v>
       </c>
       <c r="G12">
-        <v>0.107320752583561</v>
+        <v>9.7075642011394098E-2</v>
       </c>
       <c r="H12">
-        <v>0.56208374414481399</v>
+        <v>0.39068566352082501</v>
       </c>
       <c r="I12">
-        <v>0.162541288526306</v>
+        <v>0.13861770120566899</v>
       </c>
       <c r="J12">
-        <v>0.63904221867308397</v>
+        <v>0.37890487981315601</v>
       </c>
       <c r="K12">
-        <v>0.10605114685077401</v>
+        <v>9.1429190206160499E-2</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -1226,31 +1193,31 @@
         <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D13">
-        <v>0.525816074948803</v>
+        <v>0.552125688741675</v>
       </c>
       <c r="E13">
-        <v>0.130821853174137</v>
+        <v>6.2198395975696E-2</v>
       </c>
       <c r="F13">
-        <v>0.580717512616024</v>
+        <v>0.36382661198595001</v>
       </c>
       <c r="G13">
-        <v>0.170998825215809</v>
+        <v>0.12587649066721501</v>
       </c>
       <c r="H13">
-        <v>0.55877349600931803</v>
+        <v>0.40720793713228098</v>
       </c>
       <c r="I13">
-        <v>0.16608305592702299</v>
+        <v>0.152003546407599</v>
       </c>
       <c r="J13">
-        <v>0.65493555800730996</v>
+        <v>0.35757693928352402</v>
       </c>
       <c r="K13">
-        <v>0.24094998417636801</v>
+        <v>0.14620931982392399</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -1264,28 +1231,28 @@
         <v>12</v>
       </c>
       <c r="D14">
-        <v>0.57064276464486097</v>
+        <v>0.85466648466956296</v>
       </c>
       <c r="E14">
-        <v>0.15688570126454901</v>
+        <v>0.16487366896782099</v>
       </c>
       <c r="F14">
-        <v>0.71033599676720705</v>
+        <v>0.80958805516806598</v>
       </c>
       <c r="G14">
-        <v>0.13130229677498001</v>
+        <v>0.20293057296899999</v>
       </c>
       <c r="H14">
-        <v>0.57214372142930703</v>
+        <v>0.86613726602382302</v>
       </c>
       <c r="I14">
-        <v>0.15672794631897599</v>
+        <v>0.21913846302265</v>
       </c>
       <c r="J14">
-        <v>0.98158346607185598</v>
+        <v>0.79035162655523805</v>
       </c>
       <c r="K14">
-        <v>9.8457779656192998E-2</v>
+        <v>0.22976229030078499</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
@@ -1296,31 +1263,31 @@
         <v>15</v>
       </c>
       <c r="C15" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D15">
-        <v>0.54241653106482002</v>
+        <v>0.69280270966151003</v>
       </c>
       <c r="E15">
-        <v>9.9695239609421199E-2</v>
+        <v>0.13607993269257701</v>
       </c>
       <c r="F15">
-        <v>0.65851481199260797</v>
+        <v>0.55715799098594199</v>
       </c>
       <c r="G15">
-        <v>0.106976625397685</v>
+        <v>0.181761527468916</v>
       </c>
       <c r="H15">
-        <v>0.57488108783354297</v>
+        <v>0.68388457543514802</v>
       </c>
       <c r="I15">
-        <v>0.15253706896897201</v>
+        <v>0.215989929342635</v>
       </c>
       <c r="J15">
-        <v>0.81843268895355503</v>
+        <v>0.54964965655092601</v>
       </c>
       <c r="K15">
-        <v>0.13788916100913001</v>
+        <v>0.25568645803733803</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
@@ -1334,28 +1301,28 @@
         <v>14</v>
       </c>
       <c r="D16">
-        <v>0.52685766152931002</v>
+        <v>0.54057531270774395</v>
       </c>
       <c r="E16">
-        <v>6.2584987975028802E-2</v>
+        <v>6.8665641139284403E-2</v>
       </c>
       <c r="F16">
-        <v>0.60627727670711595</v>
+        <v>0.38999787452335999</v>
       </c>
       <c r="G16">
-        <v>9.1513319372480306E-2</v>
+        <v>8.1644846940611401E-2</v>
       </c>
       <c r="H16">
-        <v>0.58069691805744506</v>
+        <v>0.41060419345028798</v>
       </c>
       <c r="I16">
-        <v>0.15384886292220701</v>
+        <v>0.115620904909361</v>
       </c>
       <c r="J16">
-        <v>0.66645919192838299</v>
+        <v>0.39959706971678299</v>
       </c>
       <c r="K16">
-        <v>8.9050753200833693E-2</v>
+        <v>0.113499062440691</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
@@ -1366,31 +1333,31 @@
         <v>15</v>
       </c>
       <c r="C17" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D17">
-        <v>0.507630634253182</v>
+        <v>0.56187310934489598</v>
       </c>
       <c r="E17">
-        <v>8.7909570354966604E-2</v>
+        <v>8.7628909256180804E-2</v>
       </c>
       <c r="F17">
-        <v>0.57183412555366397</v>
+        <v>0.37351172403448701</v>
       </c>
       <c r="G17">
-        <v>0.142122960048781</v>
+        <v>0.116578047420766</v>
       </c>
       <c r="H17">
-        <v>0.571214040635739</v>
+        <v>0.43540828318757502</v>
       </c>
       <c r="I17">
-        <v>0.152726663924596</v>
+        <v>0.13178666285401999</v>
       </c>
       <c r="J17">
-        <v>0.65186769301034597</v>
+        <v>0.37157055520718901</v>
       </c>
       <c r="K17">
-        <v>0.24831029688433501</v>
+        <v>0.162108189596366</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
@@ -1404,28 +1371,28 @@
         <v>12</v>
       </c>
       <c r="D18">
-        <v>0.57547065337763004</v>
+        <v>0.67737843551796995</v>
       </c>
       <c r="E18">
-        <v>0.16202159721913001</v>
+        <v>0.123927218089982</v>
       </c>
       <c r="F18">
-        <v>0.66843853820597998</v>
+        <v>0.64116464930418404</v>
       </c>
       <c r="G18">
-        <v>0.190922161346191</v>
+        <v>0.19654630331856099</v>
       </c>
       <c r="H18">
-        <v>0.55116279069767404</v>
+        <v>0.60043373938722699</v>
       </c>
       <c r="I18">
-        <v>0.193178076822453</v>
+        <v>0.227092016908643</v>
       </c>
       <c r="J18">
-        <v>0.89534883720930203</v>
+        <v>0.74022702104097404</v>
       </c>
       <c r="K18">
-        <v>0.24051316749599799</v>
+        <v>0.23850014824455101</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
@@ -1436,31 +1403,31 @@
         <v>19</v>
       </c>
       <c r="C19" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D19">
-        <v>0.50143964562569199</v>
+        <v>0.60317124735729299</v>
       </c>
       <c r="E19">
-        <v>0.22922809622939999</v>
+        <v>0.13984813323298101</v>
       </c>
       <c r="F19">
-        <v>0.55339608711701704</v>
+        <v>0.47561171158982302</v>
       </c>
       <c r="G19">
-        <v>0.28313767464999601</v>
+        <v>0.236715114231451</v>
       </c>
       <c r="H19">
-        <v>0.47286821705426302</v>
+        <v>0.53482834994462902</v>
       </c>
       <c r="I19">
-        <v>0.25962165017175698</v>
+        <v>0.30542434893259901</v>
       </c>
       <c r="J19">
-        <v>0.70155038759689903</v>
+        <v>0.49332779623477202</v>
       </c>
       <c r="K19">
-        <v>0.35684183834058603</v>
+        <v>0.27619657880936899</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
@@ -1471,31 +1438,31 @@
         <v>19</v>
       </c>
       <c r="C20" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D20">
-        <v>0.52295127353266802</v>
+        <v>0.56279069767441803</v>
       </c>
       <c r="E20">
-        <v>0.22533458830137801</v>
+        <v>0.15223132444594001</v>
       </c>
       <c r="F20">
-        <v>0.50645994832041297</v>
+        <v>0.42257548652897398</v>
       </c>
       <c r="G20">
-        <v>0.295515245851385</v>
+        <v>0.20859505622604399</v>
       </c>
       <c r="H20">
-        <v>0.50542635658914703</v>
+        <v>0.50868401624215498</v>
       </c>
       <c r="I20">
-        <v>0.31361691213017201</v>
+        <v>0.28600729675702602</v>
       </c>
       <c r="J20">
-        <v>0.56007751937984496</v>
+        <v>0.41459025470653299</v>
       </c>
       <c r="K20">
-        <v>0.35552377081354802</v>
+        <v>0.22813541219289599</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
@@ -1509,28 +1476,28 @@
         <v>14</v>
       </c>
       <c r="D21">
-        <v>0.47652270210409697</v>
+        <v>0.53382663847780099</v>
       </c>
       <c r="E21">
-        <v>0.26125641152965101</v>
+        <v>0.16552034541087901</v>
       </c>
       <c r="F21">
-        <v>0.49093761535621999</v>
+        <v>0.393405818987214</v>
       </c>
       <c r="G21">
-        <v>0.3068450034172</v>
+        <v>0.240990212737349</v>
       </c>
       <c r="H21">
-        <v>0.45</v>
+        <v>0.43564045773348098</v>
       </c>
       <c r="I21">
-        <v>0.296708907366452</v>
+        <v>0.30267313484868802</v>
       </c>
       <c r="J21">
-        <v>0.57945736434108497</v>
+        <v>0.41029900332225899</v>
       </c>
       <c r="K21">
-        <v>0.36961180154469497</v>
+        <v>0.27033776703829598</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
@@ -1544,28 +1511,28 @@
         <v>12</v>
       </c>
       <c r="D22">
-        <v>0.57364329976444095</v>
+        <v>0.85363003512300595</v>
       </c>
       <c r="E22">
-        <v>0.15344494243187601</v>
+        <v>0.165645588770511</v>
       </c>
       <c r="F22">
-        <v>0.71713335153609803</v>
+        <v>0.80856124120930695</v>
       </c>
       <c r="G22">
-        <v>0.119914757257268</v>
+        <v>0.203572333578589</v>
       </c>
       <c r="H22">
-        <v>0.57507701148514301</v>
+        <v>0.86249131589477002</v>
       </c>
       <c r="I22">
-        <v>0.154144337447158</v>
+        <v>0.22049079030863999</v>
       </c>
       <c r="J22">
-        <v>0.99510503067619105</v>
+        <v>0.791390310607336</v>
       </c>
       <c r="K22">
-        <v>1.5764428063470899E-2</v>
+        <v>0.22985131087163699</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
@@ -1576,31 +1543,31 @@
         <v>19</v>
       </c>
       <c r="C23" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D23">
-        <v>0.56204869859593398</v>
+        <v>0.67037104551878701</v>
       </c>
       <c r="E23">
-        <v>0.123722907764762</v>
+        <v>0.13010802104640801</v>
       </c>
       <c r="F23">
-        <v>0.67142661234990697</v>
+        <v>0.54118599852220595</v>
       </c>
       <c r="G23">
-        <v>0.12128971593910901</v>
+        <v>0.18321508465967601</v>
       </c>
       <c r="H23">
-        <v>0.58236804898311301</v>
+        <v>0.59955249429564605</v>
       </c>
       <c r="I23">
-        <v>0.155437440950565</v>
+        <v>0.21882464125429801</v>
       </c>
       <c r="J23">
-        <v>0.84046950237130302</v>
+        <v>0.54451903006762004</v>
       </c>
       <c r="K23">
-        <v>0.14859184456567101</v>
+        <v>0.231472985958177</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
@@ -1614,28 +1581,28 @@
         <v>14</v>
       </c>
       <c r="D24">
-        <v>0.52066807286107597</v>
+        <v>0.56743694091200003</v>
       </c>
       <c r="E24">
-        <v>7.6460770975846498E-2</v>
+        <v>5.5625078076333101E-2</v>
       </c>
       <c r="F24">
-        <v>0.58756875468690895</v>
+        <v>0.40220735989049999</v>
       </c>
       <c r="G24">
-        <v>0.109036511658375</v>
+        <v>9.9590743367545101E-2</v>
       </c>
       <c r="H24">
-        <v>0.57699603031364299</v>
+        <v>0.431881222720497</v>
       </c>
       <c r="I24">
-        <v>0.16239638892973601</v>
+        <v>0.14164866479048299</v>
       </c>
       <c r="J24">
-        <v>0.62880939304238703</v>
+        <v>0.39280146573922697</v>
       </c>
       <c r="K24">
-        <v>0.107588276281826</v>
+        <v>9.4829181261848694E-2</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
@@ -1646,31 +1613,31 @@
         <v>19</v>
       </c>
       <c r="C25" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D25">
-        <v>0.515140102251747</v>
+        <v>0.58694372241257298</v>
       </c>
       <c r="E25">
-        <v>0.13658056818619699</v>
+        <v>8.0022526758134205E-2</v>
       </c>
       <c r="F25">
-        <v>0.55333732516781498</v>
+        <v>0.39193897370108099</v>
       </c>
       <c r="G25">
-        <v>0.18106232706957201</v>
+        <v>0.124492251254636</v>
       </c>
       <c r="H25">
-        <v>0.54496361522441505</v>
+        <v>0.46471816213351302</v>
       </c>
       <c r="I25">
-        <v>0.17539157761606</v>
+        <v>0.170386333931385</v>
       </c>
       <c r="J25">
-        <v>0.60095836504550304</v>
+        <v>0.36870245614632502</v>
       </c>
       <c r="K25">
-        <v>0.22808419906146499</v>
+        <v>0.145357955707487</v>
       </c>
     </row>
   </sheetData>
@@ -1730,70 +1697,70 @@
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B2" s="32" t="s">
+      <c r="B2" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="32" t="s">
+      <c r="D2" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="35" t="s">
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="I2" s="36"/>
-      <c r="J2" s="36"/>
-      <c r="K2" s="37"/>
-      <c r="L2" s="35" t="s">
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="29"/>
+      <c r="L2" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="M2" s="36"/>
-      <c r="N2" s="36"/>
-      <c r="O2" s="37"/>
+      <c r="M2" s="28"/>
+      <c r="N2" s="28"/>
+      <c r="O2" s="29"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B3" s="40"/>
-      <c r="C3" s="13" t="s">
+      <c r="B3" s="32"/>
+      <c r="C3" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="G3" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="K3" s="13" t="s">
+      <c r="K3" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="L3" s="12" t="s">
+      <c r="L3" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="M3" s="7" t="s">
+      <c r="M3" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="N3" s="7" t="s">
+      <c r="N3" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="O3" s="13" t="s">
+      <c r="O3" s="10" t="s">
         <v>24</v>
       </c>
     </row>
@@ -1801,300 +1768,300 @@
       <c r="A4" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="38" t="s">
+      <c r="B4" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="3" t="str">
+      <c r="D4" s="13" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C4,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A4)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C4,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A4)*100,2),"0.00")</f>
-        <v>54.2417 ± 9.97</v>
-      </c>
-      <c r="E4" s="2" t="str">
+        <v>56.1873 ± 8.76</v>
+      </c>
+      <c r="E4" s="7" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C4,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A4)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C4,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A4)*100,2),"0.00")</f>
-        <v>65.8515 ± 10.70</v>
-      </c>
-      <c r="F4" s="2" t="str">
+        <v>37.3512 ± 11.66</v>
+      </c>
+      <c r="F4" s="7" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C4,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A4)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C4,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A4)*100,2),"0.00")</f>
-        <v>57.4881 ± 15.25</v>
-      </c>
-      <c r="G4" s="5" t="str">
+        <v>43.5408 ± 13.18</v>
+      </c>
+      <c r="G4" s="14" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C4,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A4)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C4,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A4)*100,2),"0.00")</f>
-        <v>81.8433 ± 13.79</v>
-      </c>
-      <c r="H4" s="3" t="str">
+        <v>37.1571 ± 16.21</v>
+      </c>
+      <c r="H4" s="13" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C4,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A4)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C4,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A4)*100,2),"0.00")</f>
-        <v>56.2049 ± 12.37</v>
-      </c>
-      <c r="I4" s="2" t="str">
+        <v>58.6944 ± 8.00</v>
+      </c>
+      <c r="I4" s="7" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C4,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A4)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C4,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A4)*100,2),"0.00")</f>
-        <v>67.1427 ± 12.13</v>
-      </c>
-      <c r="J4" s="9" t="str">
+        <v>39.1939 ± 12.45</v>
+      </c>
+      <c r="J4" s="7" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C4,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A4)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C4,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A4)*100,2),"0.00")</f>
-        <v>58.2368 ± 15.54</v>
-      </c>
-      <c r="K4" s="5" t="str">
+        <v>46.4718 ± 17.04</v>
+      </c>
+      <c r="K4" s="14" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C4,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A4)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C4,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A4)*100,2),"0.00")</f>
-        <v>84.0470 ± 14.86</v>
-      </c>
-      <c r="L4" s="3" t="str">
+        <v>36.8702 ± 14.54</v>
+      </c>
+      <c r="L4" s="13" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C4,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A4)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C4,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A4)*100,2),"0.00")</f>
-        <v>54.1485 ± 10.34</v>
-      </c>
-      <c r="M4" s="2" t="str">
+        <v>55.2126 ± 6.22</v>
+      </c>
+      <c r="M4" s="7" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C4,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A4)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C4,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A4)*100,2),"0.00")</f>
-        <v>64.7458 ± 11.59</v>
-      </c>
-      <c r="N4" s="9" t="str">
+        <v>36.3827 ± 12.59</v>
+      </c>
+      <c r="N4" s="7" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C4,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A4)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C4,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A4)*100,2),"0.00")</f>
-        <v>57.4418 ± 15.31</v>
-      </c>
-      <c r="O4" s="5" t="str">
+        <v>40.7208 ± 15.20</v>
+      </c>
+      <c r="O4" s="14" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C4,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A4)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C4,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A4)*100,2),"0.00")</f>
-        <v>78.7743 ± 14.73</v>
+        <v>35.7577 ± 14.62</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="38"/>
-      <c r="C5" s="28" t="s">
+      <c r="B5" s="30"/>
+      <c r="C5" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="14" t="str">
+      <c r="D5" s="11" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C5,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A5)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C5,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A5)*100,2),"0.00")</f>
-        <v>50.7631 ± 8.79</v>
+        <v>69.2803 ± 13.61</v>
       </c>
       <c r="E5" s="8" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C5,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A5)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C5,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A5)*100,2),"0.00")</f>
-        <v>57.1834 ± 14.21</v>
-      </c>
-      <c r="F5" s="11" t="str">
+        <v>55.7158 ± 18.18</v>
+      </c>
+      <c r="F5" s="8" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C5,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A5)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C5,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A5)*100,2),"0.00")</f>
-        <v>57.1214 ± 15.27</v>
-      </c>
-      <c r="G5" s="15" t="str">
+        <v>68.3885 ± 21.60</v>
+      </c>
+      <c r="G5" s="12" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C5,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A5)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C5,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A5)*100,2),"0.00")</f>
-        <v>65.1868 ± 24.83</v>
-      </c>
-      <c r="H5" s="14" t="str">
+        <v>54.9650 ± 25.57</v>
+      </c>
+      <c r="H5" s="11" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C5,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A5)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C5,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A5)*100,2),"0.00")</f>
-        <v>51.5140 ± 13.66</v>
+        <v>67.0371 ± 13.01</v>
       </c>
       <c r="I5" s="8" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C5,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A5)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C5,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A5)*100,2),"0.00")</f>
-        <v>55.3337 ± 18.11</v>
+        <v>54.1186 ± 18.32</v>
       </c>
       <c r="J5" s="8" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C5,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A5)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C5,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A5)*100,2),"0.00")</f>
-        <v>54.4964 ± 17.54</v>
-      </c>
-      <c r="K5" s="15" t="str">
+        <v>59.9552 ± 21.88</v>
+      </c>
+      <c r="K5" s="12" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C5,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A5)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C5,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A5)*100,2),"0.00")</f>
-        <v>60.0958 ± 22.81</v>
-      </c>
-      <c r="L5" s="14" t="str">
+        <v>54.4519 ± 23.15</v>
+      </c>
+      <c r="L5" s="11" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C5,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A5)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C5,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A5)*100,2),"0.00")</f>
-        <v>52.5816 ± 13.08</v>
+        <v>62.1516 ± 13.47</v>
       </c>
       <c r="M5" s="8" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C5,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A5)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C5,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A5)*100,2),"0.00")</f>
-        <v>58.0718 ± 17.10</v>
+        <v>49.0434 ± 17.62</v>
       </c>
       <c r="N5" s="8" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C5,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A5)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C5,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A5)*100,2),"0.00")</f>
-        <v>55.8773 ± 16.61</v>
-      </c>
-      <c r="O5" s="15" t="str">
+        <v>54.7530 ± 22.07</v>
+      </c>
+      <c r="O5" s="12" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C5,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A5)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C5,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A5)*100,2),"0.00")</f>
-        <v>65.4936 ± 24.09</v>
+        <v>52.7360 ± 26.84</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="38"/>
-      <c r="C6" s="4" t="s">
+      <c r="B6" s="30"/>
+      <c r="C6" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="26" t="str">
+      <c r="D6" s="18" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C6,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A6)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C6,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A6)*100,2),"0.00")</f>
-        <v>57.0643 ± 15.69</v>
-      </c>
-      <c r="E6" s="9" t="str">
+        <v>85.4666 ± 16.49</v>
+      </c>
+      <c r="E6" s="6" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C6,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A6)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C6,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A6)*100,2),"0.00")</f>
-        <v>71.0336 ± 13.13</v>
-      </c>
-      <c r="F6" s="2" t="str">
+        <v>80.9588 ± 20.29</v>
+      </c>
+      <c r="F6" s="6" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C6,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A6)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C6,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A6)*100,2),"0.00")</f>
-        <v>57.2144 ± 15.67</v>
-      </c>
-      <c r="G6" s="27" t="str">
+        <v>86.6137 ± 21.91</v>
+      </c>
+      <c r="G6" s="19" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C6,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A6)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C6,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A6)*100,2),"0.00")</f>
-        <v>98.1583 ± 9.85</v>
-      </c>
-      <c r="H6" s="26" t="str">
+        <v>79.0352 ± 22.98</v>
+      </c>
+      <c r="H6" s="18" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C6,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A6)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C6,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A6)*100,2),"0.00")</f>
-        <v>57.3643 ± 15.34</v>
-      </c>
-      <c r="I6" s="9" t="str">
+        <v>85.3630 ± 16.56</v>
+      </c>
+      <c r="I6" s="6" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C6,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A6)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C6,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A6)*100,2),"0.00")</f>
-        <v>71.7133 ± 11.99</v>
-      </c>
-      <c r="J6" s="10" t="str">
+        <v>80.8561 ± 20.36</v>
+      </c>
+      <c r="J6" s="6" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C6,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A6)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C6,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A6)*100,2),"0.00")</f>
-        <v>57.5077 ± 15.41</v>
-      </c>
-      <c r="K6" s="27" t="str">
+        <v>86.2491 ± 22.05</v>
+      </c>
+      <c r="K6" s="19" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C6,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A6)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C6,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A6)*100,2),"0.00")</f>
-        <v>99.5105 ± 1.58</v>
-      </c>
-      <c r="L6" s="26" t="str">
+        <v>79.1390 ± 22.99</v>
+      </c>
+      <c r="L6" s="18" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C6,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A6)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C6,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A6)*100,2),"0.00")</f>
-        <v>57.0783 ± 15.49</v>
-      </c>
-      <c r="M6" s="9" t="str">
+        <v>85.4768 ± 16.45</v>
+      </c>
+      <c r="M6" s="6" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C6,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A6)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C6,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A6)*100,2),"0.00")</f>
-        <v>71.0873 ± 12.61</v>
-      </c>
-      <c r="N6" s="10" t="str">
+        <v>80.9368 ± 20.24</v>
+      </c>
+      <c r="N6" s="6" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C6,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A6)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C6,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A6)*100,2),"0.00")</f>
-        <v>57.2857 ± 15.53</v>
-      </c>
-      <c r="O6" s="27" t="str">
+        <v>86.6137 ± 21.91</v>
+      </c>
+      <c r="O6" s="19" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C6,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A6)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C6,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A6)*100,2),"0.00")</f>
-        <v>97.8653 ± 7.59</v>
+        <v>78.9702 ± 22.84</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="39"/>
-      <c r="C7" s="29" t="s">
+      <c r="B7" s="31"/>
+      <c r="C7" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="16" t="str">
+      <c r="D7" s="15" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C7,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A7)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C7,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A7)*100,2),"0.00")</f>
-        <v>52.6858 ± 6.26</v>
-      </c>
-      <c r="E7" s="17" t="str">
+        <v>54.0575 ± 6.87</v>
+      </c>
+      <c r="E7" s="16" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C7,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A7)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C7,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A7)*100,2),"0.00")</f>
-        <v>60.6277 ± 9.15</v>
-      </c>
-      <c r="F7" s="41" t="str">
+        <v>38.9998 ± 8.16</v>
+      </c>
+      <c r="F7" s="16" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C7,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A7)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C7,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A7)*100,2),"0.00")</f>
-        <v>58.0697 ± 15.38</v>
-      </c>
-      <c r="G7" s="18" t="str">
+        <v>41.0604 ± 11.56</v>
+      </c>
+      <c r="G7" s="17" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C7,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A7)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C7,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A7)*100,2),"0.00")</f>
-        <v>66.6459 ± 8.91</v>
-      </c>
-      <c r="H7" s="16" t="str">
+        <v>39.9597 ± 11.35</v>
+      </c>
+      <c r="H7" s="15" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C7,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A7)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C7,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A7)*100,2),"0.00")</f>
-        <v>52.0668 ± 7.65</v>
-      </c>
-      <c r="I7" s="17" t="str">
+        <v>56.7437 ± 5.56</v>
+      </c>
+      <c r="I7" s="16" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C7,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A7)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C7,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A7)*100,2),"0.00")</f>
-        <v>58.7569 ± 10.90</v>
-      </c>
-      <c r="J7" s="17" t="str">
+        <v>40.2207 ± 9.96</v>
+      </c>
+      <c r="J7" s="16" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C7,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A7)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C7,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A7)*100,2),"0.00")</f>
-        <v>57.6996 ± 16.24</v>
-      </c>
-      <c r="K7" s="18" t="str">
+        <v>43.1881 ± 14.16</v>
+      </c>
+      <c r="K7" s="17" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C7,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A7)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C7,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A7)*100,2),"0.00")</f>
-        <v>62.8809 ± 10.76</v>
-      </c>
-      <c r="L7" s="16" t="str">
+        <v>39.2801 ± 9.48</v>
+      </c>
+      <c r="L7" s="15" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C7,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A7)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C7,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A7)*100,2),"0.00")</f>
-        <v>50.5841 ± 7.33</v>
-      </c>
-      <c r="M7" s="17" t="str">
+        <v>52.8502 ± 5.84</v>
+      </c>
+      <c r="M7" s="16" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C7,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A7)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C7,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A7)*100,2),"0.00")</f>
-        <v>58.4445 ± 10.73</v>
-      </c>
-      <c r="N7" s="17" t="str">
+        <v>37.5087 ± 9.71</v>
+      </c>
+      <c r="N7" s="16" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C7,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A7)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C7,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A7)*100,2),"0.00")</f>
-        <v>56.2084 ± 16.25</v>
-      </c>
-      <c r="O7" s="18" t="str">
+        <v>39.0686 ± 13.86</v>
+      </c>
+      <c r="O7" s="17" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C7,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A7)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C7,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A7)*100,2),"0.00")</f>
-        <v>63.9042 ± 10.61</v>
+        <v>37.8905 ± 9.14</v>
       </c>
     </row>
     <row r="8" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B8" s="1"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B9" s="32" t="s">
+      <c r="B9" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="30" t="s">
+      <c r="C9" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="32" t="s">
+      <c r="D9" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="E9" s="33"/>
-      <c r="F9" s="33"/>
-      <c r="G9" s="34"/>
-      <c r="H9" s="35" t="s">
+      <c r="E9" s="25"/>
+      <c r="F9" s="25"/>
+      <c r="G9" s="26"/>
+      <c r="H9" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="I9" s="36"/>
-      <c r="J9" s="36"/>
-      <c r="K9" s="37"/>
-      <c r="L9" s="35" t="s">
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
+      <c r="K9" s="29"/>
+      <c r="L9" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="M9" s="36"/>
-      <c r="N9" s="36"/>
-      <c r="O9" s="37"/>
+      <c r="M9" s="28"/>
+      <c r="N9" s="28"/>
+      <c r="O9" s="29"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B10" s="40"/>
-      <c r="C10" s="31" t="s">
+      <c r="B10" s="32"/>
+      <c r="C10" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G10" s="13" t="s">
+      <c r="G10" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="H10" s="12" t="s">
+      <c r="H10" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I10" s="7" t="s">
+      <c r="I10" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="J10" s="7" t="s">
+      <c r="J10" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="K10" s="13" t="s">
+      <c r="K10" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="L10" s="12" t="s">
+      <c r="L10" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="M10" s="7" t="s">
+      <c r="M10" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="N10" s="7" t="s">
+      <c r="N10" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="O10" s="13" t="s">
+      <c r="O10" s="10" t="s">
         <v>24</v>
       </c>
     </row>
@@ -2102,230 +2069,230 @@
       <c r="A11" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="38" t="s">
+      <c r="B11" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="21" t="str">
+      <c r="D11" s="13" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C11,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A11)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C11,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A11)*100,2),"0.00")</f>
-        <v>51.9158 ± 21.01</v>
-      </c>
-      <c r="E11" s="10" t="str">
+        <v>54.1860 ± 13.88</v>
+      </c>
+      <c r="E11" s="7" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C11,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A11)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C11,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A11)*100,2),"0.00")</f>
-        <v>57.7538 ± 21.82</v>
-      </c>
-      <c r="F11" s="10" t="str">
+        <v>40.9197 ± 19.44</v>
+      </c>
+      <c r="F11" s="7" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C11,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A11)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C11,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A11)*100,2),"0.00")</f>
-        <v>53.1395 ± 22.11</v>
-      </c>
-      <c r="G11" s="22" t="str">
+        <v>45.8029 ± 23.66</v>
+      </c>
+      <c r="G11" s="14" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C11,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A11)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C11,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A11)*100,2),"0.00")</f>
-        <v>68.6047 ± 28.97</v>
-      </c>
-      <c r="H11" s="21" t="str">
+        <v>41.6944 ± 22.90</v>
+      </c>
+      <c r="H11" s="13" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C11,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A11)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C11,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A11)*100,2),"0.00")</f>
-        <v>50.1440 ± 22.92</v>
-      </c>
-      <c r="I11" s="10" t="str">
+        <v>56.2791 ± 15.22</v>
+      </c>
+      <c r="I11" s="7" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C11,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A11)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C11,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A11)*100,2),"0.00")</f>
-        <v>55.3396 ± 28.31</v>
-      </c>
-      <c r="J11" s="10" t="str">
+        <v>42.2575 ± 20.86</v>
+      </c>
+      <c r="J11" s="7" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C11,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A11)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C11,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A11)*100,2),"0.00")</f>
-        <v>47.2868 ± 25.96</v>
-      </c>
-      <c r="K11" s="22" t="str">
+        <v>50.8684 ± 28.60</v>
+      </c>
+      <c r="K11" s="14" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C11,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A11)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C11,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A11)*100,2),"0.00")</f>
-        <v>70.1550 ± 35.68</v>
-      </c>
-      <c r="L11" s="21" t="str">
+        <v>41.4590 ± 22.81</v>
+      </c>
+      <c r="L11" s="13" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C11,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A11)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C11,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A11)*100,2),"0.00")</f>
-        <v>52.1872 ± 21.97</v>
-      </c>
-      <c r="M11" s="10" t="str">
+        <v>51.3953 ± 13.04</v>
+      </c>
+      <c r="M11" s="7" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C11,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A11)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C11,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A11)*100,2),"0.00")</f>
-        <v>59.3079 ± 23.40</v>
-      </c>
-      <c r="N11" s="9" t="str">
+        <v>34.9427 ± 23.21</v>
+      </c>
+      <c r="N11" s="7" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C11,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A11)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C11,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A11)*100,2),"0.00")</f>
-        <v>52.2093 ± 23.92</v>
-      </c>
-      <c r="O11" s="22" t="str">
+        <v>38.1035 ± 27.68</v>
+      </c>
+      <c r="O11" s="14" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C11,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A11)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C11,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A11)*100,2),"0.00")</f>
-        <v>74.0310 ± 30.93</v>
+        <v>36.1240 ± 24.12</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="38"/>
-      <c r="C12" s="28" t="s">
+      <c r="B12" s="30"/>
+      <c r="C12" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="D12" s="19" t="str">
+      <c r="D12" s="11" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C12,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A12)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C12,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A12)*100,2),"0.00")</f>
-        <v>54.5875 ± 22.10</v>
-      </c>
-      <c r="E12" s="11" t="str">
+        <v>61.8605 ± 14.71</v>
+      </c>
+      <c r="E12" s="8" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C12,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A12)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C12,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A12)*100,2),"0.00")</f>
-        <v>56.9878 ± 25.52</v>
-      </c>
-      <c r="F12" s="11" t="str">
+        <v>48.6599 ± 23.06</v>
+      </c>
+      <c r="F12" s="8" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C12,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A12)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C12,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A12)*100,2),"0.00")</f>
-        <v>54.1860 ± 25.55</v>
-      </c>
-      <c r="G12" s="20" t="str">
+        <v>57.3145 ± 28.02</v>
+      </c>
+      <c r="G12" s="12" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C12,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A12)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C12,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A12)*100,2),"0.00")</f>
-        <v>64.5349 ± 31.75</v>
-      </c>
-      <c r="H12" s="19" t="str">
+        <v>49.0255 ± 28.32</v>
+      </c>
+      <c r="H12" s="11" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C12,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A12)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C12,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A12)*100,2),"0.00")</f>
-        <v>52.2951 ± 22.53</v>
-      </c>
-      <c r="I12" s="11" t="str">
+        <v>60.3171 ± 13.98</v>
+      </c>
+      <c r="I12" s="8" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C12,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A12)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C12,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A12)*100,2),"0.00")</f>
-        <v>50.6460 ± 29.55</v>
-      </c>
-      <c r="J12" s="11" t="str">
+        <v>47.5612 ± 23.67</v>
+      </c>
+      <c r="J12" s="8" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C12,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A12)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C12,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A12)*100,2),"0.00")</f>
-        <v>50.5426 ± 31.36</v>
-      </c>
-      <c r="K12" s="20" t="str">
+        <v>53.4828 ± 30.54</v>
+      </c>
+      <c r="K12" s="12" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C12,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A12)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C12,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A12)*100,2),"0.00")</f>
-        <v>56.0078 ± 35.55</v>
-      </c>
-      <c r="L12" s="43" t="str">
+        <v>49.3328 ± 27.62</v>
+      </c>
+      <c r="L12" s="11" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C12,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A12)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C12,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A12)*100,2),"0.00")</f>
-        <v>52.8378 ± 25.10</v>
-      </c>
-      <c r="M12" s="11" t="str">
+        <v>56.6808 ± 13.02</v>
+      </c>
+      <c r="M12" s="8" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C12,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A12)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C12,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A12)*100,2),"0.00")</f>
-        <v>53.2041 ± 31.52</v>
-      </c>
-      <c r="N12" s="11" t="str">
+        <v>39.5943 ± 23.84</v>
+      </c>
+      <c r="N12" s="8" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C12,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A12)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C12,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A12)*100,2),"0.00")</f>
-        <v>48.1395 ± 29.90</v>
-      </c>
-      <c r="O12" s="20" t="str">
+        <v>44.1787 ± 30.93</v>
+      </c>
+      <c r="O12" s="12" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C12,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A12)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C12,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A12)*100,2),"0.00")</f>
-        <v>62.2093 ± 37.24</v>
+        <v>42.0930 ± 28.55</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="38"/>
-      <c r="C13" s="4" t="s">
+      <c r="B13" s="30"/>
+      <c r="C13" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="21" t="str">
+      <c r="D13" s="18" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C13,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A13)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C13,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A13)*100,2),"0.00")</f>
-        <v>47.7243 ± 23.20</v>
-      </c>
-      <c r="E13" s="10" t="str">
+        <v>72.4524 ± 12.63</v>
+      </c>
+      <c r="E13" s="6" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C13,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A13)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C13,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A13)*100,2),"0.00")</f>
-        <v>56.8316 ± 25.33</v>
-      </c>
-      <c r="F13" s="10" t="str">
+        <v>70.7934 ± 14.24</v>
+      </c>
+      <c r="F13" s="6" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C13,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A13)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C13,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A13)*100,2),"0.00")</f>
-        <v>48.5770 ± 24.58</v>
-      </c>
-      <c r="G13" s="27" t="str">
+        <v>65.8084 ± 17.76</v>
+      </c>
+      <c r="G13" s="19" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C13,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A13)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C13,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A13)*100,2),"0.00")</f>
-        <v>74.8062 ± 34.69</v>
-      </c>
-      <c r="H13" s="26" t="str">
+        <v>81.9961 ± 17.53</v>
+      </c>
+      <c r="H13" s="18" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C13,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A13)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C13,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A13)*100,2),"0.00")</f>
-        <v>57.5471 ± 16.20</v>
-      </c>
-      <c r="I13" s="9" t="str">
+        <v>67.7378 ± 12.39</v>
+      </c>
+      <c r="I13" s="6" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C13,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A13)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C13,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A13)*100,2),"0.00")</f>
-        <v>66.8439 ± 19.09</v>
-      </c>
-      <c r="J13" s="9" t="str">
+        <v>64.1165 ± 19.65</v>
+      </c>
+      <c r="J13" s="6" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C13,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A13)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C13,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A13)*100,2),"0.00")</f>
-        <v>55.1163 ± 19.32</v>
-      </c>
-      <c r="K13" s="27" t="str">
+        <v>60.0434 ± 22.71</v>
+      </c>
+      <c r="K13" s="19" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C13,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A13)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C13,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A13)*100,2),"0.00")</f>
-        <v>89.5349 ± 24.05</v>
-      </c>
-      <c r="L13" s="21" t="str">
+        <v>74.0227 ± 23.85</v>
+      </c>
+      <c r="L13" s="18" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C13,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A13)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C13,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A13)*100,2),"0.00")</f>
-        <v>52.4142 ± 22.11</v>
-      </c>
-      <c r="M13" s="9" t="str">
+        <v>70.9937 ± 12.25</v>
+      </c>
+      <c r="M13" s="6" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C13,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A13)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C13,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A13)*100,2),"0.00")</f>
-        <v>60.8442 ± 25.33</v>
-      </c>
-      <c r="N13" s="10" t="str">
+        <v>69.3429 ± 13.72</v>
+      </c>
+      <c r="N13" s="6" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C13,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A13)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C13,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A13)*100,2),"0.00")</f>
-        <v>50.5537 ± 23.21</v>
-      </c>
-      <c r="O13" s="27" t="str">
+        <v>65.0914 ± 18.56</v>
+      </c>
+      <c r="O13" s="19" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C13,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A13)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C13,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A13)*100,2),"0.00")</f>
-        <v>80.4264 ± 32.94</v>
+        <v>80.5842 ± 18.34</v>
       </c>
     </row>
     <row r="14" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="39"/>
-      <c r="C14" s="29" t="s">
+      <c r="B14" s="31"/>
+      <c r="C14" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="D14" s="42" t="str">
+      <c r="D14" s="15" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C14,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A14)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C14,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A14)*100,2),"0.00")</f>
-        <v>55.9828 ± 22.33</v>
-      </c>
-      <c r="E14" s="41" t="str">
+        <v>52.7484 ± 14.18</v>
+      </c>
+      <c r="E14" s="16" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C14,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A14)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C14,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A14)*100,2),"0.00")</f>
-        <v>61.1683 ± 21.81</v>
-      </c>
-      <c r="F14" s="41" t="str">
+        <v>37.6273 ± 23.75</v>
+      </c>
+      <c r="F14" s="16" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C14,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A14)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C14,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A14)*100,2),"0.00")</f>
-        <v>58.4496 ± 24.15</v>
-      </c>
-      <c r="G14" s="25" t="str">
+        <v>42.0543 ± 26.72</v>
+      </c>
+      <c r="G14" s="17" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C14,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A14)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C14,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A14)*100,2),"0.00")</f>
-        <v>71.1240 ± 29.44</v>
-      </c>
-      <c r="H14" s="23" t="str">
+        <v>38.4109 ± 28.09</v>
+      </c>
+      <c r="H14" s="15" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C14,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A14)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C14,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A14)*100,2),"0.00")</f>
-        <v>47.6523 ± 26.13</v>
-      </c>
-      <c r="I14" s="24" t="str">
+        <v>53.3827 ± 16.55</v>
+      </c>
+      <c r="I14" s="16" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C14,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A14)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C14,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A14)*100,2),"0.00")</f>
-        <v>49.0938 ± 30.68</v>
-      </c>
-      <c r="J14" s="24" t="str">
+        <v>39.3406 ± 24.10</v>
+      </c>
+      <c r="J14" s="16" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C14,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A14)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C14,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A14)*100,2),"0.00")</f>
-        <v>45.0000 ± 29.67</v>
-      </c>
-      <c r="K14" s="25" t="str">
+        <v>43.5640 ± 30.27</v>
+      </c>
+      <c r="K14" s="17" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C14,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A14)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C14,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A14)*100,2),"0.00")</f>
-        <v>57.9457 ± 36.96</v>
-      </c>
-      <c r="L14" s="23" t="str">
+        <v>41.0299 ± 27.03</v>
+      </c>
+      <c r="L14" s="15" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C14,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A14)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C14,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A14)*100,2),"0.00")</f>
-        <v>49.2027 ± 22.38</v>
-      </c>
-      <c r="M14" s="24" t="str">
+        <v>49.4503 ± 10.85</v>
+      </c>
+      <c r="M14" s="16" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C14,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A14)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C14,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A14)*100,2),"0.00")</f>
-        <v>53.8649 ± 24.97</v>
-      </c>
-      <c r="N14" s="24" t="str">
+        <v>33.8395 ± 17.87</v>
+      </c>
+      <c r="N14" s="16" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C14,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A14)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C14,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A14)*100,2),"0.00")</f>
-        <v>49.4574 ± 25.32</v>
-      </c>
-      <c r="O14" s="25" t="str">
+        <v>37.3533 ± 20.61</v>
+      </c>
+      <c r="O14" s="17" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C14,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A14)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C14,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A14)*100,2),"0.00")</f>
-        <v>63.9535 ± 32.93</v>
+        <v>35.5592 ± 22.74</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Comparison.xlsx
+++ b/Results/Comparison.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nikoo\Desktop\Thesis\Source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94857F76-471F-42AA-84BD-98EE4C7B8BBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB3A8288-FD37-490F-B4C5-C95FB82C014B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{8D592C9F-CC51-43DD-B2E3-0BF015735963}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$K$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$K$17</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="30">
   <si>
     <t>Model</t>
   </si>
@@ -93,9 +93,6 @@
     <t>Agg</t>
   </si>
   <si>
-    <t>Win</t>
-  </si>
-  <si>
     <t>Raw + VG</t>
   </si>
   <si>
@@ -130,9 +127,6 @@
   </si>
   <si>
     <t>Run Mode</t>
-  </si>
-  <si>
-    <t>Windowed</t>
   </si>
   <si>
     <t>Aggregated</t>
@@ -341,9 +335,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -418,6 +409,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -754,7 +748,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20B60A1F-9449-4A91-8C37-2E569624DE33}">
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" bestFit="1" customWidth="1"/>
@@ -811,28 +805,28 @@
         <v>12</v>
       </c>
       <c r="D2">
-        <v>0.72452431289640495</v>
+        <v>0.55749354005167895</v>
       </c>
       <c r="E2">
-        <v>0.12634112205655601</v>
+        <v>0.15348326060099099</v>
       </c>
       <c r="F2">
-        <v>0.70793418467836999</v>
+        <v>0.633120368004089</v>
       </c>
       <c r="G2">
-        <v>0.14239179692925599</v>
+        <v>0.15377250914937199</v>
       </c>
       <c r="H2">
-        <v>0.65808416389811697</v>
+        <v>0.52490771502399403</v>
       </c>
       <c r="I2">
-        <v>0.17755312426902001</v>
+        <v>0.16668560240673699</v>
       </c>
       <c r="J2">
-        <v>0.819961240310077</v>
+        <v>0.86057585825027605</v>
       </c>
       <c r="K2">
-        <v>0.17530527934034201</v>
+        <v>0.17675025732223501</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
@@ -846,28 +840,28 @@
         <v>13</v>
       </c>
       <c r="D3">
-        <v>0.61860465116278995</v>
+        <v>0.56524547803617498</v>
       </c>
       <c r="E3">
-        <v>0.147057152906341</v>
+        <v>0.157805312148043</v>
       </c>
       <c r="F3">
-        <v>0.48659854357528698</v>
+        <v>0.51837852070410195</v>
       </c>
       <c r="G3">
-        <v>0.23057853355097499</v>
+        <v>0.21897253334531999</v>
       </c>
       <c r="H3">
-        <v>0.57314507198228104</v>
+        <v>0.524750830564784</v>
       </c>
       <c r="I3">
-        <v>0.28022744816873202</v>
+        <v>0.23180912179789501</v>
       </c>
       <c r="J3">
-        <v>0.49025470653377601</v>
+        <v>0.58903654485049795</v>
       </c>
       <c r="K3">
-        <v>0.28321899195455902</v>
+        <v>0.30886126361202598</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
@@ -878,31 +872,31 @@
         <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D4">
-        <v>0.54186046511627906</v>
+        <v>0.44573643410852698</v>
       </c>
       <c r="E4">
-        <v>0.13878941103190401</v>
+        <v>0.144020632520451</v>
       </c>
       <c r="F4">
-        <v>0.40919700454584101</v>
+        <v>0.457372730628544</v>
       </c>
       <c r="G4">
-        <v>0.19444552422140901</v>
+        <v>0.17671043523787699</v>
       </c>
       <c r="H4">
-        <v>0.45802879291251303</v>
+        <v>0.41925987449243202</v>
       </c>
       <c r="I4">
-        <v>0.236613898616195</v>
+        <v>0.16986342000034901</v>
       </c>
       <c r="J4">
-        <v>0.41694352159468401</v>
+        <v>0.56589147286821695</v>
       </c>
       <c r="K4">
-        <v>0.22895421142504299</v>
+        <v>0.26108384429446602</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
@@ -913,31 +907,31 @@
         <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D5">
-        <v>0.52748414376321295</v>
+        <v>0.51227390180878496</v>
       </c>
       <c r="E5">
-        <v>0.14176732936727399</v>
+        <v>0.16343796917110201</v>
       </c>
       <c r="F5">
-        <v>0.376273080924243</v>
+        <v>0.43721433605154503</v>
       </c>
       <c r="G5">
-        <v>0.23752310296649501</v>
+        <v>0.21692111966841199</v>
       </c>
       <c r="H5">
-        <v>0.42054263565891398</v>
+        <v>0.484274640088593</v>
       </c>
       <c r="I5">
-        <v>0.26718885416195898</v>
+        <v>0.289640857037127</v>
       </c>
       <c r="J5">
-        <v>0.38410852713178201</v>
+        <v>0.46788482834994399</v>
       </c>
       <c r="K5">
-        <v>0.28085462990170401</v>
+        <v>0.267991474667366</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
@@ -945,34 +939,34 @@
         <v>16</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
         <v>12</v>
       </c>
       <c r="D6">
-        <v>0.70993657505285401</v>
+        <v>0.56007751937984496</v>
       </c>
       <c r="E6">
-        <v>0.12249902749579</v>
+        <v>0.16339711095498999</v>
       </c>
       <c r="F6">
-        <v>0.69342853528899995</v>
+        <v>0.62272985412520299</v>
       </c>
       <c r="G6">
-        <v>0.13723894892184399</v>
+        <v>0.18710077850829199</v>
       </c>
       <c r="H6">
-        <v>0.650913621262458</v>
+        <v>0.52248984865263903</v>
       </c>
       <c r="I6">
-        <v>0.18556441073274901</v>
+        <v>0.18390591881927101</v>
       </c>
       <c r="J6">
-        <v>0.805841638981173</v>
+        <v>0.83189368770764105</v>
       </c>
       <c r="K6">
-        <v>0.18342370490437901</v>
+        <v>0.247371425901838</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
@@ -980,34 +974,34 @@
         <v>16</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
         <v>13</v>
       </c>
       <c r="D7">
-        <v>0.56680761099365695</v>
+        <v>0.52131782945736405</v>
       </c>
       <c r="E7">
-        <v>0.13022672346282799</v>
+        <v>0.17443535186131501</v>
       </c>
       <c r="F7">
-        <v>0.39594346222253202</v>
+        <v>0.43456491828584798</v>
       </c>
       <c r="G7">
-        <v>0.238376007132796</v>
+        <v>0.242920266636416</v>
       </c>
       <c r="H7">
-        <v>0.441786637135474</v>
+        <v>0.46484865263934999</v>
       </c>
       <c r="I7">
-        <v>0.30926351009386199</v>
+        <v>0.29316204016411401</v>
       </c>
       <c r="J7">
-        <v>0.42093023255813899</v>
+        <v>0.480121816168327</v>
       </c>
       <c r="K7">
-        <v>0.28549020288911198</v>
+        <v>0.30601421298699899</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
@@ -1015,34 +1009,34 @@
         <v>16</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D8">
-        <v>0.51395348837209298</v>
+        <v>0.46091731266149799</v>
       </c>
       <c r="E8">
-        <v>0.130381082765363</v>
+        <v>0.18749714836460701</v>
       </c>
       <c r="F8">
-        <v>0.34942680058959102</v>
+        <v>0.43192053424611498</v>
       </c>
       <c r="G8">
-        <v>0.232072836102137</v>
+        <v>0.21289700431233999</v>
       </c>
       <c r="H8">
-        <v>0.38103543743078599</v>
+        <v>0.43169988925802799</v>
       </c>
       <c r="I8">
-        <v>0.276812031560489</v>
+        <v>0.23655927930680301</v>
       </c>
       <c r="J8">
-        <v>0.361240310077519</v>
+        <v>0.48964562569213699</v>
       </c>
       <c r="K8">
-        <v>0.24117735218907199</v>
+        <v>0.25908269364331399</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
@@ -1050,39 +1044,39 @@
         <v>16</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D9">
-        <v>0.49450317124735699</v>
+        <v>0.44864341085271298</v>
       </c>
       <c r="E9">
-        <v>0.10854584647769699</v>
+        <v>0.184513245718608</v>
       </c>
       <c r="F9">
-        <v>0.33839493839493801</v>
+        <v>0.36692842041679202</v>
       </c>
       <c r="G9">
-        <v>0.17867296269323699</v>
+        <v>0.23346928268556499</v>
       </c>
       <c r="H9">
-        <v>0.37353266888150599</v>
+        <v>0.38433001107419701</v>
       </c>
       <c r="I9">
-        <v>0.20606682582033001</v>
+        <v>0.27197080272274599</v>
       </c>
       <c r="J9">
-        <v>0.35559246954595702</v>
+        <v>0.396400885935769</v>
       </c>
       <c r="K9">
-        <v>0.22738182713701699</v>
+        <v>0.27895538753580901</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>18</v>
@@ -1091,564 +1085,144 @@
         <v>12</v>
       </c>
       <c r="D10">
-        <v>0.85476754021099299</v>
+        <v>0.51550387596899205</v>
       </c>
       <c r="E10">
-        <v>0.164461385373316</v>
+        <v>0.17251811765168401</v>
       </c>
       <c r="F10">
-        <v>0.80936807219704598</v>
+        <v>0.59471665285618702</v>
       </c>
       <c r="G10">
-        <v>0.20241393067035701</v>
+        <v>0.18753211096234301</v>
       </c>
       <c r="H10">
-        <v>0.86613726602382302</v>
+        <v>0.49889258028792899</v>
       </c>
       <c r="I10">
-        <v>0.21913846302265</v>
+        <v>0.20636506381518299</v>
       </c>
       <c r="J10">
-        <v>0.78970169273031898</v>
+        <v>0.80404208194905802</v>
       </c>
       <c r="K10">
-        <v>0.228405686826789</v>
+        <v>0.20711232758545101</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D11">
-        <v>0.62151622960802899</v>
+        <v>0.53197674418604601</v>
       </c>
       <c r="E11">
-        <v>0.13468267500880399</v>
+        <v>0.18117650340232599</v>
       </c>
       <c r="F11">
-        <v>0.49043386633550401</v>
+        <v>0.49334076775937202</v>
       </c>
       <c r="G11">
-        <v>0.17615792337158401</v>
+        <v>0.178552174200312</v>
       </c>
       <c r="H11">
-        <v>0.54753001969928705</v>
+        <v>0.55495570321151699</v>
       </c>
       <c r="I11">
-        <v>0.22074265292426901</v>
+        <v>0.24335929593338099</v>
       </c>
       <c r="J11">
-        <v>0.52735964681776903</v>
+        <v>0.51561461794019903</v>
       </c>
       <c r="K11">
-        <v>0.26838495731504902</v>
+        <v>0.219269172902882</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D12">
-        <v>0.52850216899770497</v>
+        <v>0.53133074935400504</v>
       </c>
       <c r="E12">
-        <v>5.83606083461716E-2</v>
+        <v>0.155617057772441</v>
       </c>
       <c r="F12">
-        <v>0.37508689676345702</v>
+        <v>0.44240785054738502</v>
       </c>
       <c r="G12">
-        <v>9.7075642011394098E-2</v>
+        <v>0.21885537992434601</v>
       </c>
       <c r="H12">
-        <v>0.39068566352082501</v>
+        <v>0.51589147286821702</v>
       </c>
       <c r="I12">
-        <v>0.13861770120566899</v>
+        <v>0.29171789544013399</v>
       </c>
       <c r="J12">
-        <v>0.37890487981315601</v>
+        <v>0.44158361018826098</v>
       </c>
       <c r="K12">
-        <v>9.1429190206160499E-2</v>
+        <v>0.246619473264934</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D13">
-        <v>0.552125688741675</v>
+        <v>0.48191214470284199</v>
       </c>
       <c r="E13">
-        <v>6.2198395975696E-2</v>
+        <v>0.21119980804774</v>
       </c>
       <c r="F13">
-        <v>0.36382661198595001</v>
+        <v>0.404829924597366</v>
       </c>
       <c r="G13">
-        <v>0.12587649066721501</v>
+        <v>0.288242341868583</v>
       </c>
       <c r="H13">
-        <v>0.40720793713228098</v>
+        <v>0.440669988925802</v>
       </c>
       <c r="I13">
-        <v>0.152003546407599</v>
+        <v>0.325237869278242</v>
       </c>
       <c r="J13">
-        <v>0.35757693928352402</v>
+        <v>0.42059800664451802</v>
       </c>
       <c r="K13">
-        <v>0.14620931982392399</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14">
-        <v>0.85466648466956296</v>
-      </c>
-      <c r="E14">
-        <v>0.16487366896782099</v>
-      </c>
-      <c r="F14">
-        <v>0.80958805516806598</v>
-      </c>
-      <c r="G14">
-        <v>0.20293057296899999</v>
-      </c>
-      <c r="H14">
-        <v>0.86613726602382302</v>
-      </c>
-      <c r="I14">
-        <v>0.21913846302265</v>
-      </c>
-      <c r="J14">
-        <v>0.79035162655523805</v>
-      </c>
-      <c r="K14">
-        <v>0.22976229030078499</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" t="s">
-        <v>13</v>
-      </c>
-      <c r="D15">
-        <v>0.69280270966151003</v>
-      </c>
-      <c r="E15">
-        <v>0.13607993269257701</v>
-      </c>
-      <c r="F15">
-        <v>0.55715799098594199</v>
-      </c>
-      <c r="G15">
-        <v>0.181761527468916</v>
-      </c>
-      <c r="H15">
-        <v>0.68388457543514802</v>
-      </c>
-      <c r="I15">
-        <v>0.215989929342635</v>
-      </c>
-      <c r="J15">
-        <v>0.54964965655092601</v>
-      </c>
-      <c r="K15">
-        <v>0.25568645803733803</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C16" t="s">
-        <v>14</v>
-      </c>
-      <c r="D16">
-        <v>0.54057531270774395</v>
-      </c>
-      <c r="E16">
-        <v>6.8665641139284403E-2</v>
-      </c>
-      <c r="F16">
-        <v>0.38999787452335999</v>
-      </c>
-      <c r="G16">
-        <v>8.1644846940611401E-2</v>
-      </c>
-      <c r="H16">
-        <v>0.41060419345028798</v>
-      </c>
-      <c r="I16">
-        <v>0.115620904909361</v>
-      </c>
-      <c r="J16">
-        <v>0.39959706971678299</v>
-      </c>
-      <c r="K16">
-        <v>0.113499062440691</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C17" t="s">
-        <v>11</v>
-      </c>
-      <c r="D17">
-        <v>0.56187310934489598</v>
-      </c>
-      <c r="E17">
-        <v>8.7628909256180804E-2</v>
-      </c>
-      <c r="F17">
-        <v>0.37351172403448701</v>
-      </c>
-      <c r="G17">
-        <v>0.116578047420766</v>
-      </c>
-      <c r="H17">
-        <v>0.43540828318757502</v>
-      </c>
-      <c r="I17">
-        <v>0.13178666285401999</v>
-      </c>
-      <c r="J17">
-        <v>0.37157055520718901</v>
-      </c>
-      <c r="K17">
-        <v>0.162108189596366</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C18" t="s">
-        <v>12</v>
-      </c>
-      <c r="D18">
-        <v>0.67737843551796995</v>
-      </c>
-      <c r="E18">
-        <v>0.123927218089982</v>
-      </c>
-      <c r="F18">
-        <v>0.64116464930418404</v>
-      </c>
-      <c r="G18">
-        <v>0.19654630331856099</v>
-      </c>
-      <c r="H18">
-        <v>0.60043373938722699</v>
-      </c>
-      <c r="I18">
-        <v>0.227092016908643</v>
-      </c>
-      <c r="J18">
-        <v>0.74022702104097404</v>
-      </c>
-      <c r="K18">
-        <v>0.23850014824455101</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D19">
-        <v>0.60317124735729299</v>
-      </c>
-      <c r="E19">
-        <v>0.13984813323298101</v>
-      </c>
-      <c r="F19">
-        <v>0.47561171158982302</v>
-      </c>
-      <c r="G19">
-        <v>0.236715114231451</v>
-      </c>
-      <c r="H19">
-        <v>0.53482834994462902</v>
-      </c>
-      <c r="I19">
-        <v>0.30542434893259901</v>
-      </c>
-      <c r="J19">
-        <v>0.49332779623477202</v>
-      </c>
-      <c r="K19">
-        <v>0.27619657880936899</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C20" t="s">
-        <v>11</v>
-      </c>
-      <c r="D20">
-        <v>0.56279069767441803</v>
-      </c>
-      <c r="E20">
-        <v>0.15223132444594001</v>
-      </c>
-      <c r="F20">
-        <v>0.42257548652897398</v>
-      </c>
-      <c r="G20">
-        <v>0.20859505622604399</v>
-      </c>
-      <c r="H20">
-        <v>0.50868401624215498</v>
-      </c>
-      <c r="I20">
-        <v>0.28600729675702602</v>
-      </c>
-      <c r="J20">
-        <v>0.41459025470653299</v>
-      </c>
-      <c r="K20">
-        <v>0.22813541219289599</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C21" t="s">
-        <v>14</v>
-      </c>
-      <c r="D21">
-        <v>0.53382663847780099</v>
-      </c>
-      <c r="E21">
-        <v>0.16552034541087901</v>
-      </c>
-      <c r="F21">
-        <v>0.393405818987214</v>
-      </c>
-      <c r="G21">
-        <v>0.240990212737349</v>
-      </c>
-      <c r="H21">
-        <v>0.43564045773348098</v>
-      </c>
-      <c r="I21">
-        <v>0.30267313484868802</v>
-      </c>
-      <c r="J21">
-        <v>0.41029900332225899</v>
-      </c>
-      <c r="K21">
-        <v>0.27033776703829598</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C22" t="s">
-        <v>12</v>
-      </c>
-      <c r="D22">
-        <v>0.85363003512300595</v>
-      </c>
-      <c r="E22">
-        <v>0.165645588770511</v>
-      </c>
-      <c r="F22">
-        <v>0.80856124120930695</v>
-      </c>
-      <c r="G22">
-        <v>0.203572333578589</v>
-      </c>
-      <c r="H22">
-        <v>0.86249131589477002</v>
-      </c>
-      <c r="I22">
-        <v>0.22049079030863999</v>
-      </c>
-      <c r="J22">
-        <v>0.791390310607336</v>
-      </c>
-      <c r="K22">
-        <v>0.22985131087163699</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C23" t="s">
-        <v>13</v>
-      </c>
-      <c r="D23">
-        <v>0.67037104551878701</v>
-      </c>
-      <c r="E23">
-        <v>0.13010802104640801</v>
-      </c>
-      <c r="F23">
-        <v>0.54118599852220595</v>
-      </c>
-      <c r="G23">
-        <v>0.18321508465967601</v>
-      </c>
-      <c r="H23">
-        <v>0.59955249429564605</v>
-      </c>
-      <c r="I23">
-        <v>0.21882464125429801</v>
-      </c>
-      <c r="J23">
-        <v>0.54451903006762004</v>
-      </c>
-      <c r="K23">
-        <v>0.231472985958177</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C24" t="s">
-        <v>14</v>
-      </c>
-      <c r="D24">
-        <v>0.56743694091200003</v>
-      </c>
-      <c r="E24">
-        <v>5.5625078076333101E-2</v>
-      </c>
-      <c r="F24">
-        <v>0.40220735989049999</v>
-      </c>
-      <c r="G24">
-        <v>9.9590743367545101E-2</v>
-      </c>
-      <c r="H24">
-        <v>0.431881222720497</v>
-      </c>
-      <c r="I24">
-        <v>0.14164866479048299</v>
-      </c>
-      <c r="J24">
-        <v>0.39280146573922697</v>
-      </c>
-      <c r="K24">
-        <v>9.4829181261848694E-2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C25" t="s">
-        <v>11</v>
-      </c>
-      <c r="D25">
-        <v>0.58694372241257298</v>
-      </c>
-      <c r="E25">
-        <v>8.0022526758134205E-2</v>
-      </c>
-      <c r="F25">
-        <v>0.39193897370108099</v>
-      </c>
-      <c r="G25">
-        <v>0.124492251254636</v>
-      </c>
-      <c r="H25">
-        <v>0.46471816213351302</v>
-      </c>
-      <c r="I25">
-        <v>0.170386333931385</v>
-      </c>
-      <c r="J25">
-        <v>0.36870245614632502</v>
-      </c>
-      <c r="K25">
-        <v>0.145357955707487</v>
+        <v>0.31620061780796399</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K25" xr:uid="{20B60A1F-9449-4A91-8C37-2E569624DE33}"/>
+  <autoFilter ref="A1:K17" xr:uid="{20B60A1F-9449-4A91-8C37-2E569624DE33}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{926F4F26-DE01-4BB2-9AB3-84FA32AC1323}">
-  <dimension ref="A1:O14"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.88671875" customWidth="1"/>
@@ -1672,643 +1246,337 @@
         <v>15</v>
       </c>
       <c r="H1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L1" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N1" t="s">
+        <v>17</v>
+      </c>
+      <c r="O1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B2" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="I2" s="27"/>
+      <c r="J2" s="27"/>
+      <c r="K2" s="28"/>
+      <c r="L2" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="M2" s="27"/>
+      <c r="N2" s="27"/>
+      <c r="O2" s="28"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B3" s="31"/>
+      <c r="C3" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="I1" t="s">
-        <v>19</v>
-      </c>
-      <c r="J1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1" t="s">
-        <v>19</v>
-      </c>
-      <c r="L1" t="s">
-        <v>18</v>
-      </c>
-      <c r="M1" t="s">
-        <v>18</v>
-      </c>
-      <c r="N1" t="s">
-        <v>18</v>
-      </c>
-      <c r="O1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B2" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D2" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="I2" s="28"/>
-      <c r="J2" s="28"/>
-      <c r="K2" s="29"/>
-      <c r="L2" s="27" t="s">
-        <v>28</v>
-      </c>
-      <c r="M2" s="28"/>
-      <c r="N2" s="28"/>
-      <c r="O2" s="29"/>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B3" s="32"/>
-      <c r="C3" s="10" t="s">
+      <c r="D3" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="E3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="F3" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="G3" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="J3" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="K3" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="K3" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="L3" s="9" t="s">
+      <c r="L3" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="M3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M3" s="5" t="s">
+      <c r="N3" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="N3" s="5" t="s">
+      <c r="O3" s="9" t="s">
         <v>23</v>
-      </c>
-      <c r="O3" s="10" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="30" t="s">
-        <v>30</v>
+        <v>16</v>
+      </c>
+      <c r="B4" s="29" t="s">
+        <v>29</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="13" t="str">
+      <c r="D4" s="12" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C4,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A4)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C4,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A4)*100,2),"0.00")</f>
-        <v>56.1873 ± 8.76</v>
-      </c>
-      <c r="E4" s="7" t="str">
+        <v>51.2274 ± 16.34</v>
+      </c>
+      <c r="E4" s="6" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C4,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A4)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C4,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A4)*100,2),"0.00")</f>
-        <v>37.3512 ± 11.66</v>
-      </c>
-      <c r="F4" s="7" t="str">
+        <v>43.7214 ± 21.69</v>
+      </c>
+      <c r="F4" s="6" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C4,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A4)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C4,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A4)*100,2),"0.00")</f>
-        <v>43.5408 ± 13.18</v>
-      </c>
-      <c r="G4" s="14" t="str">
+        <v>48.4275 ± 28.96</v>
+      </c>
+      <c r="G4" s="13" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C4,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A4)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C4,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A4)*100,2),"0.00")</f>
-        <v>37.1571 ± 16.21</v>
-      </c>
-      <c r="H4" s="13" t="str">
+        <v>46.7885 ± 26.80</v>
+      </c>
+      <c r="H4" s="17" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C4,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A4)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C4,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A4)*100,2),"0.00")</f>
-        <v>58.6944 ± 8.00</v>
-      </c>
-      <c r="I4" s="7" t="str">
+        <v>53.1977 ± 18.12</v>
+      </c>
+      <c r="I4" s="6" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C4,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A4)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C4,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A4)*100,2),"0.00")</f>
-        <v>39.1939 ± 12.45</v>
-      </c>
-      <c r="J4" s="7" t="str">
+        <v>49.3341 ± 17.86</v>
+      </c>
+      <c r="J4" s="5" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C4,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A4)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C4,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A4)*100,2),"0.00")</f>
-        <v>46.4718 ± 17.04</v>
-      </c>
-      <c r="K4" s="14" t="str">
+        <v>55.4956 ± 24.34</v>
+      </c>
+      <c r="K4" s="13" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C4,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A4)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C4,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A4)*100,2),"0.00")</f>
-        <v>36.8702 ± 14.54</v>
-      </c>
-      <c r="L4" s="13" t="str">
+        <v>51.5615 ± 21.93</v>
+      </c>
+      <c r="L4" s="12" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C4,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A4)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C4,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A4)*100,2),"0.00")</f>
-        <v>55.2126 ± 6.22</v>
-      </c>
-      <c r="M4" s="7" t="str">
+        <v>44.8643 ± 18.45</v>
+      </c>
+      <c r="M4" s="6" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C4,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A4)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C4,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A4)*100,2),"0.00")</f>
-        <v>36.3827 ± 12.59</v>
-      </c>
-      <c r="N4" s="7" t="str">
+        <v>36.6928 ± 23.35</v>
+      </c>
+      <c r="N4" s="6" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C4,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A4)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C4,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A4)*100,2),"0.00")</f>
-        <v>40.7208 ± 15.20</v>
-      </c>
-      <c r="O4" s="14" t="str">
+        <v>38.4330 ± 27.20</v>
+      </c>
+      <c r="O4" s="13" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C4,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A4)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C4,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A4)*100,2),"0.00")</f>
-        <v>35.7577 ± 14.62</v>
+        <v>39.6401 ± 27.90</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="30"/>
-      <c r="C5" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="29"/>
+      <c r="C5" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="11" t="str">
+      <c r="D5" s="32" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C5,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A5)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C5,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A5)*100,2),"0.00")</f>
-        <v>69.2803 ± 13.61</v>
-      </c>
-      <c r="E5" s="8" t="str">
+        <v>56.5245 ± 15.78</v>
+      </c>
+      <c r="E5" s="7" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C5,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A5)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C5,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A5)*100,2),"0.00")</f>
-        <v>55.7158 ± 18.18</v>
-      </c>
-      <c r="F5" s="8" t="str">
+        <v>51.8379 ± 21.90</v>
+      </c>
+      <c r="F5" s="7" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C5,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A5)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C5,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A5)*100,2),"0.00")</f>
-        <v>68.3885 ± 21.60</v>
-      </c>
-      <c r="G5" s="12" t="str">
+        <v>52.4751 ± 23.18</v>
+      </c>
+      <c r="G5" s="11" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C5,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A5)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C5,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A5)*100,2),"0.00")</f>
-        <v>54.9650 ± 25.57</v>
-      </c>
-      <c r="H5" s="11" t="str">
+        <v>58.9037 ± 30.89</v>
+      </c>
+      <c r="H5" s="10" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C5,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A5)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C5,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A5)*100,2),"0.00")</f>
-        <v>67.0371 ± 13.01</v>
-      </c>
-      <c r="I5" s="8" t="str">
+        <v>53.1331 ± 15.56</v>
+      </c>
+      <c r="I5" s="7" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C5,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A5)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C5,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A5)*100,2),"0.00")</f>
-        <v>54.1186 ± 18.32</v>
-      </c>
-      <c r="J5" s="8" t="str">
+        <v>44.2408 ± 21.89</v>
+      </c>
+      <c r="J5" s="7" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C5,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A5)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C5,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A5)*100,2),"0.00")</f>
-        <v>59.9552 ± 21.88</v>
-      </c>
-      <c r="K5" s="12" t="str">
+        <v>51.5891 ± 29.17</v>
+      </c>
+      <c r="K5" s="11" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C5,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A5)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C5,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A5)*100,2),"0.00")</f>
-        <v>54.4519 ± 23.15</v>
-      </c>
-      <c r="L5" s="11" t="str">
+        <v>44.1584 ± 24.66</v>
+      </c>
+      <c r="L5" s="10" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C5,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A5)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C5,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A5)*100,2),"0.00")</f>
-        <v>62.1516 ± 13.47</v>
-      </c>
-      <c r="M5" s="8" t="str">
+        <v>52.1318 ± 17.44</v>
+      </c>
+      <c r="M5" s="7" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C5,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A5)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C5,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A5)*100,2),"0.00")</f>
-        <v>49.0434 ± 17.62</v>
-      </c>
-      <c r="N5" s="8" t="str">
+        <v>43.4565 ± 24.29</v>
+      </c>
+      <c r="N5" s="7" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C5,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A5)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C5,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A5)*100,2),"0.00")</f>
-        <v>54.7530 ± 22.07</v>
-      </c>
-      <c r="O5" s="12" t="str">
+        <v>46.4849 ± 29.32</v>
+      </c>
+      <c r="O5" s="11" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C5,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A5)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C5,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A5)*100,2),"0.00")</f>
-        <v>52.7360 ± 26.84</v>
+        <v>48.0122 ± 30.60</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="30"/>
+        <v>16</v>
+      </c>
+      <c r="B6" s="29"/>
       <c r="C6" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="18" t="str">
+      <c r="D6" s="12" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C6,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A6)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C6,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A6)*100,2),"0.00")</f>
-        <v>85.4666 ± 16.49</v>
-      </c>
-      <c r="E6" s="6" t="str">
+        <v>55.7494 ± 15.35</v>
+      </c>
+      <c r="E6" s="5" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C6,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A6)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C6,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A6)*100,2),"0.00")</f>
-        <v>80.9588 ± 20.29</v>
-      </c>
-      <c r="F6" s="6" t="str">
+        <v>63.3120 ± 15.38</v>
+      </c>
+      <c r="F6" s="5" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C6,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A6)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C6,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A6)*100,2),"0.00")</f>
-        <v>86.6137 ± 21.91</v>
-      </c>
-      <c r="G6" s="19" t="str">
+        <v>52.4908 ± 16.67</v>
+      </c>
+      <c r="G6" s="18" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C6,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A6)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C6,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A6)*100,2),"0.00")</f>
-        <v>79.0352 ± 22.98</v>
-      </c>
-      <c r="H6" s="18" t="str">
+        <v>86.0576 ± 17.68</v>
+      </c>
+      <c r="H6" s="12" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C6,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A6)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C6,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A6)*100,2),"0.00")</f>
-        <v>85.3630 ± 16.56</v>
-      </c>
-      <c r="I6" s="6" t="str">
+        <v>51.5504 ± 17.25</v>
+      </c>
+      <c r="I6" s="5" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C6,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A6)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C6,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A6)*100,2),"0.00")</f>
-        <v>80.8561 ± 20.36</v>
+        <v>59.4717 ± 18.75</v>
       </c>
       <c r="J6" s="6" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C6,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A6)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C6,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A6)*100,2),"0.00")</f>
-        <v>86.2491 ± 22.05</v>
-      </c>
-      <c r="K6" s="19" t="str">
+        <v>49.8893 ± 20.64</v>
+      </c>
+      <c r="K6" s="18" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C6,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A6)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C6,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A6)*100,2),"0.00")</f>
-        <v>79.1390 ± 22.99</v>
-      </c>
-      <c r="L6" s="18" t="str">
+        <v>80.4042 ± 20.71</v>
+      </c>
+      <c r="L6" s="17" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C6,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A6)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C6,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A6)*100,2),"0.00")</f>
-        <v>85.4768 ± 16.45</v>
-      </c>
-      <c r="M6" s="6" t="str">
+        <v>56.0078 ± 16.34</v>
+      </c>
+      <c r="M6" s="5" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C6,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A6)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C6,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A6)*100,2),"0.00")</f>
-        <v>80.9368 ± 20.24</v>
-      </c>
-      <c r="N6" s="6" t="str">
+        <v>62.2730 ± 18.71</v>
+      </c>
+      <c r="N6" s="5" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C6,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A6)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C6,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A6)*100,2),"0.00")</f>
-        <v>86.6137 ± 21.91</v>
-      </c>
-      <c r="O6" s="19" t="str">
+        <v>52.2490 ± 18.39</v>
+      </c>
+      <c r="O6" s="18" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C6,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A6)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C6,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A6)*100,2),"0.00")</f>
-        <v>78.9702 ± 22.84</v>
+        <v>83.1894 ± 24.74</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="31"/>
-      <c r="C7" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="30"/>
+      <c r="C7" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="15" t="str">
+      <c r="D7" s="14" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C7,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A7)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C7,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A7)*100,2),"0.00")</f>
-        <v>54.0575 ± 6.87</v>
-      </c>
-      <c r="E7" s="16" t="str">
+        <v>44.5736 ± 14.40</v>
+      </c>
+      <c r="E7" s="15" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C7,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A7)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C7,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A7)*100,2),"0.00")</f>
-        <v>38.9998 ± 8.16</v>
-      </c>
-      <c r="F7" s="16" t="str">
+        <v>45.7373 ± 17.67</v>
+      </c>
+      <c r="F7" s="15" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C7,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A7)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C7,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A7)*100,2),"0.00")</f>
-        <v>41.0604 ± 11.56</v>
-      </c>
-      <c r="G7" s="17" t="str">
+        <v>41.9260 ± 16.99</v>
+      </c>
+      <c r="G7" s="16" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C7,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A7)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C7,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A7)*100,2),"0.00")</f>
-        <v>39.9597 ± 11.35</v>
-      </c>
-      <c r="H7" s="15" t="str">
+        <v>56.5891 ± 26.11</v>
+      </c>
+      <c r="H7" s="14" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C7,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A7)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C7,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A7)*100,2),"0.00")</f>
-        <v>56.7437 ± 5.56</v>
-      </c>
-      <c r="I7" s="16" t="str">
+        <v>48.1912 ± 21.12</v>
+      </c>
+      <c r="I7" s="15" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C7,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A7)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C7,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A7)*100,2),"0.00")</f>
-        <v>40.2207 ± 9.96</v>
-      </c>
-      <c r="J7" s="16" t="str">
+        <v>40.4830 ± 28.82</v>
+      </c>
+      <c r="J7" s="15" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C7,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A7)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C7,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A7)*100,2),"0.00")</f>
-        <v>43.1881 ± 14.16</v>
-      </c>
-      <c r="K7" s="17" t="str">
+        <v>44.0670 ± 32.52</v>
+      </c>
+      <c r="K7" s="16" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C7,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A7)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C7,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A7)*100,2),"0.00")</f>
-        <v>39.2801 ± 9.48</v>
-      </c>
-      <c r="L7" s="15" t="str">
+        <v>42.0598 ± 31.62</v>
+      </c>
+      <c r="L7" s="14" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C7,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A7)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C7,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A7)*100,2),"0.00")</f>
-        <v>52.8502 ± 5.84</v>
-      </c>
-      <c r="M7" s="16" t="str">
+        <v>46.0917 ± 18.75</v>
+      </c>
+      <c r="M7" s="15" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C7,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A7)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C7,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A7)*100,2),"0.00")</f>
-        <v>37.5087 ± 9.71</v>
-      </c>
-      <c r="N7" s="16" t="str">
+        <v>43.1921 ± 21.29</v>
+      </c>
+      <c r="N7" s="15" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C7,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A7)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C7,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A7)*100,2),"0.00")</f>
-        <v>39.0686 ± 13.86</v>
-      </c>
-      <c r="O7" s="17" t="str">
+        <v>43.1700 ± 23.66</v>
+      </c>
+      <c r="O7" s="16" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C7,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A7)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C7,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A7)*100,2),"0.00")</f>
-        <v>37.8905 ± 9.14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="1"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B9" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" s="22" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="E9" s="25"/>
-      <c r="F9" s="25"/>
-      <c r="G9" s="26"/>
-      <c r="H9" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="I9" s="28"/>
-      <c r="J9" s="28"/>
-      <c r="K9" s="29"/>
-      <c r="L9" s="27" t="s">
-        <v>28</v>
-      </c>
-      <c r="M9" s="28"/>
-      <c r="N9" s="28"/>
-      <c r="O9" s="29"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B10" s="32"/>
-      <c r="C10" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G10" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="J10" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="K10" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="L10" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="M10" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="N10" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="O10" s="10" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="30" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D11" s="13" t="str">
-        <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C11,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A11)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C11,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A11)*100,2),"0.00")</f>
-        <v>54.1860 ± 13.88</v>
-      </c>
-      <c r="E11" s="7" t="str">
-        <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C11,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A11)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C11,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A11)*100,2),"0.00")</f>
-        <v>40.9197 ± 19.44</v>
-      </c>
-      <c r="F11" s="7" t="str">
-        <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C11,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A11)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C11,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A11)*100,2),"0.00")</f>
-        <v>45.8029 ± 23.66</v>
-      </c>
-      <c r="G11" s="14" t="str">
-        <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C11,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A11)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C11,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A11)*100,2),"0.00")</f>
-        <v>41.6944 ± 22.90</v>
-      </c>
-      <c r="H11" s="13" t="str">
-        <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C11,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A11)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C11,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A11)*100,2),"0.00")</f>
-        <v>56.2791 ± 15.22</v>
-      </c>
-      <c r="I11" s="7" t="str">
-        <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C11,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A11)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C11,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A11)*100,2),"0.00")</f>
-        <v>42.2575 ± 20.86</v>
-      </c>
-      <c r="J11" s="7" t="str">
-        <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C11,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A11)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C11,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A11)*100,2),"0.00")</f>
-        <v>50.8684 ± 28.60</v>
-      </c>
-      <c r="K11" s="14" t="str">
-        <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C11,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A11)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C11,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A11)*100,2),"0.00")</f>
-        <v>41.4590 ± 22.81</v>
-      </c>
-      <c r="L11" s="13" t="str">
-        <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C11,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A11)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C11,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A11)*100,2),"0.00")</f>
-        <v>51.3953 ± 13.04</v>
-      </c>
-      <c r="M11" s="7" t="str">
-        <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C11,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A11)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C11,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A11)*100,2),"0.00")</f>
-        <v>34.9427 ± 23.21</v>
-      </c>
-      <c r="N11" s="7" t="str">
-        <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C11,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A11)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C11,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A11)*100,2),"0.00")</f>
-        <v>38.1035 ± 27.68</v>
-      </c>
-      <c r="O11" s="14" t="str">
-        <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C11,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A11)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C11,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A11)*100,2),"0.00")</f>
-        <v>36.1240 ± 24.12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="30"/>
-      <c r="C12" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="D12" s="11" t="str">
-        <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C12,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A12)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C12,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A12)*100,2),"0.00")</f>
-        <v>61.8605 ± 14.71</v>
-      </c>
-      <c r="E12" s="8" t="str">
-        <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C12,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A12)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C12,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A12)*100,2),"0.00")</f>
-        <v>48.6599 ± 23.06</v>
-      </c>
-      <c r="F12" s="8" t="str">
-        <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C12,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A12)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C12,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A12)*100,2),"0.00")</f>
-        <v>57.3145 ± 28.02</v>
-      </c>
-      <c r="G12" s="12" t="str">
-        <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C12,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A12)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C12,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A12)*100,2),"0.00")</f>
-        <v>49.0255 ± 28.32</v>
-      </c>
-      <c r="H12" s="11" t="str">
-        <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C12,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A12)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C12,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A12)*100,2),"0.00")</f>
-        <v>60.3171 ± 13.98</v>
-      </c>
-      <c r="I12" s="8" t="str">
-        <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C12,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A12)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C12,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A12)*100,2),"0.00")</f>
-        <v>47.5612 ± 23.67</v>
-      </c>
-      <c r="J12" s="8" t="str">
-        <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C12,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A12)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C12,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A12)*100,2),"0.00")</f>
-        <v>53.4828 ± 30.54</v>
-      </c>
-      <c r="K12" s="12" t="str">
-        <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C12,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A12)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C12,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A12)*100,2),"0.00")</f>
-        <v>49.3328 ± 27.62</v>
-      </c>
-      <c r="L12" s="11" t="str">
-        <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C12,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A12)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C12,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A12)*100,2),"0.00")</f>
-        <v>56.6808 ± 13.02</v>
-      </c>
-      <c r="M12" s="8" t="str">
-        <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C12,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A12)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C12,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A12)*100,2),"0.00")</f>
-        <v>39.5943 ± 23.84</v>
-      </c>
-      <c r="N12" s="8" t="str">
-        <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C12,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A12)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C12,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A12)*100,2),"0.00")</f>
-        <v>44.1787 ± 30.93</v>
-      </c>
-      <c r="O12" s="12" t="str">
-        <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C12,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A12)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C12,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A12)*100,2),"0.00")</f>
-        <v>42.0930 ± 28.55</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="30"/>
-      <c r="C13" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D13" s="18" t="str">
-        <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C13,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A13)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C13,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A13)*100,2),"0.00")</f>
-        <v>72.4524 ± 12.63</v>
-      </c>
-      <c r="E13" s="6" t="str">
-        <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C13,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A13)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C13,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A13)*100,2),"0.00")</f>
-        <v>70.7934 ± 14.24</v>
-      </c>
-      <c r="F13" s="6" t="str">
-        <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C13,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A13)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C13,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A13)*100,2),"0.00")</f>
-        <v>65.8084 ± 17.76</v>
-      </c>
-      <c r="G13" s="19" t="str">
-        <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C13,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A13)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C13,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A13)*100,2),"0.00")</f>
-        <v>81.9961 ± 17.53</v>
-      </c>
-      <c r="H13" s="18" t="str">
-        <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C13,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A13)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C13,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A13)*100,2),"0.00")</f>
-        <v>67.7378 ± 12.39</v>
-      </c>
-      <c r="I13" s="6" t="str">
-        <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C13,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A13)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C13,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A13)*100,2),"0.00")</f>
-        <v>64.1165 ± 19.65</v>
-      </c>
-      <c r="J13" s="6" t="str">
-        <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C13,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A13)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C13,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A13)*100,2),"0.00")</f>
-        <v>60.0434 ± 22.71</v>
-      </c>
-      <c r="K13" s="19" t="str">
-        <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C13,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A13)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C13,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A13)*100,2),"0.00")</f>
-        <v>74.0227 ± 23.85</v>
-      </c>
-      <c r="L13" s="18" t="str">
-        <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C13,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A13)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C13,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A13)*100,2),"0.00")</f>
-        <v>70.9937 ± 12.25</v>
-      </c>
-      <c r="M13" s="6" t="str">
-        <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C13,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A13)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C13,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A13)*100,2),"0.00")</f>
-        <v>69.3429 ± 13.72</v>
-      </c>
-      <c r="N13" s="6" t="str">
-        <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C13,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A13)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C13,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A13)*100,2),"0.00")</f>
-        <v>65.0914 ± 18.56</v>
-      </c>
-      <c r="O13" s="19" t="str">
-        <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C13,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A13)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C13,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A13)*100,2),"0.00")</f>
-        <v>80.5842 ± 18.34</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14" s="31"/>
-      <c r="C14" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="D14" s="15" t="str">
-        <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C14,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A14)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C14,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A14)*100,2),"0.00")</f>
-        <v>52.7484 ± 14.18</v>
-      </c>
-      <c r="E14" s="16" t="str">
-        <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C14,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A14)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C14,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A14)*100,2),"0.00")</f>
-        <v>37.6273 ± 23.75</v>
-      </c>
-      <c r="F14" s="16" t="str">
-        <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C14,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A14)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C14,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A14)*100,2),"0.00")</f>
-        <v>42.0543 ± 26.72</v>
-      </c>
-      <c r="G14" s="17" t="str">
-        <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C14,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A14)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C14,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A14)*100,2),"0.00")</f>
-        <v>38.4109 ± 28.09</v>
-      </c>
-      <c r="H14" s="15" t="str">
-        <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C14,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A14)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C14,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A14)*100,2),"0.00")</f>
-        <v>53.3827 ± 16.55</v>
-      </c>
-      <c r="I14" s="16" t="str">
-        <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C14,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A14)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C14,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A14)*100,2),"0.00")</f>
-        <v>39.3406 ± 24.10</v>
-      </c>
-      <c r="J14" s="16" t="str">
-        <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C14,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A14)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C14,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A14)*100,2),"0.00")</f>
-        <v>43.5640 ± 30.27</v>
-      </c>
-      <c r="K14" s="17" t="str">
-        <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C14,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A14)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C14,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A14)*100,2),"0.00")</f>
-        <v>41.0299 ± 27.03</v>
-      </c>
-      <c r="L14" s="15" t="str">
-        <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C14,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A14)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C14,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A14)*100,2),"0.00")</f>
-        <v>49.4503 ± 10.85</v>
-      </c>
-      <c r="M14" s="16" t="str">
-        <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C14,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A14)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C14,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A14)*100,2),"0.00")</f>
-        <v>33.8395 ± 17.87</v>
-      </c>
-      <c r="N14" s="16" t="str">
-        <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C14,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A14)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C14,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A14)*100,2),"0.00")</f>
-        <v>37.3533 ± 20.61</v>
-      </c>
-      <c r="O14" s="17" t="str">
-        <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C14,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A14)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C14,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A14)*100,2),"0.00")</f>
-        <v>35.5592 ± 22.74</v>
+        <v>48.9646 ± 25.91</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="5">
+    <mergeCell ref="B4:B7"/>
+    <mergeCell ref="B2:B3"/>
     <mergeCell ref="D2:G2"/>
     <mergeCell ref="H2:K2"/>
     <mergeCell ref="L2:O2"/>
-    <mergeCell ref="B4:B7"/>
-    <mergeCell ref="B11:B14"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="D9:G9"/>
-    <mergeCell ref="H9:K9"/>
-    <mergeCell ref="L9:O9"/>
   </mergeCells>
-  <conditionalFormatting sqref="D4:O7 D11:G14">
+  <conditionalFormatting sqref="D4:G7">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -2320,7 +1588,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H11:K14">
+  <conditionalFormatting sqref="H4:K7">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -2332,7 +1600,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L11:O14">
+  <conditionalFormatting sqref="L4:O7">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>

--- a/Results/Comparison.xlsx
+++ b/Results/Comparison.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nikoo\Desktop\Thesis\Source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB3A8288-FD37-490F-B4C5-C95FB82C014B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83DF8F6D-7151-4844-B26A-5101D04AAE5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{8D592C9F-CC51-43DD-B2E3-0BF015735963}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$K$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$K$25</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="32">
   <si>
     <t>Model</t>
   </si>
@@ -93,6 +93,9 @@
     <t>Agg</t>
   </si>
   <si>
+    <t>Win</t>
+  </si>
+  <si>
     <t>Raw + VG</t>
   </si>
   <si>
@@ -127,6 +130,9 @@
   </si>
   <si>
     <t>Run Mode</t>
+  </si>
+  <si>
+    <t>Windowed</t>
   </si>
   <si>
     <t>Aggregated</t>
@@ -326,7 +332,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -335,6 +341,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -409,6 +418,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -748,7 +763,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20B60A1F-9449-4A91-8C37-2E569624DE33}">
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" bestFit="1" customWidth="1"/>
@@ -939,7 +954,7 @@
         <v>16</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
         <v>12</v>
@@ -974,7 +989,7 @@
         <v>16</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
         <v>13</v>
@@ -1009,7 +1024,7 @@
         <v>16</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
         <v>14</v>
@@ -1044,7 +1059,7 @@
         <v>16</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
         <v>11</v>
@@ -1076,7 +1091,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>18</v>
@@ -1085,144 +1100,564 @@
         <v>12</v>
       </c>
       <c r="D10">
-        <v>0.51550387596899205</v>
+        <v>0.50426114728527605</v>
       </c>
       <c r="E10">
-        <v>0.17251811765168401</v>
+        <v>0.15131712264172001</v>
       </c>
       <c r="F10">
-        <v>0.59471665285618702</v>
+        <v>0.64818409825371703</v>
       </c>
       <c r="G10">
-        <v>0.18753211096234301</v>
+        <v>0.14027953261606901</v>
       </c>
       <c r="H10">
-        <v>0.49889258028792899</v>
+        <v>0.50530406401564198</v>
       </c>
       <c r="I10">
-        <v>0.20636506381518299</v>
+        <v>0.154166654131004</v>
       </c>
       <c r="J10">
-        <v>0.80404208194905802</v>
+        <v>0.96547197696228604</v>
       </c>
       <c r="K10">
-        <v>0.20711232758545101</v>
+        <v>8.1709576276789805E-2</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D11">
-        <v>0.53197674418604601</v>
+        <v>0.48813053300051501</v>
       </c>
       <c r="E11">
-        <v>0.18117650340232599</v>
+        <v>5.0153712663033499E-2</v>
       </c>
       <c r="F11">
-        <v>0.49334076775937202</v>
+        <v>0.471680412439138</v>
       </c>
       <c r="G11">
-        <v>0.178552174200312</v>
+        <v>0.110014430989287</v>
       </c>
       <c r="H11">
-        <v>0.55495570321151699</v>
+        <v>0.49698374253069399</v>
       </c>
       <c r="I11">
-        <v>0.24335929593338099</v>
+        <v>0.16816091184656701</v>
       </c>
       <c r="J11">
-        <v>0.51561461794019903</v>
+        <v>0.481285133967431</v>
       </c>
       <c r="K11">
-        <v>0.219269172902882</v>
+        <v>0.105555248284908</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C12" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D12">
-        <v>0.53133074935400504</v>
+        <v>0.48651251712173699</v>
       </c>
       <c r="E12">
-        <v>0.155617057772441</v>
+        <v>6.1300611664400699E-2</v>
       </c>
       <c r="F12">
-        <v>0.44240785054738502</v>
+        <v>0.45756225620271102</v>
       </c>
       <c r="G12">
-        <v>0.21885537992434601</v>
+        <v>0.110687080845892</v>
       </c>
       <c r="H12">
-        <v>0.51589147286821702</v>
+        <v>0.49912411602183598</v>
       </c>
       <c r="I12">
-        <v>0.29171789544013399</v>
+        <v>0.158689431148544</v>
       </c>
       <c r="J12">
-        <v>0.44158361018826098</v>
+        <v>0.47108630420465097</v>
       </c>
       <c r="K12">
-        <v>0.246619473264934</v>
+        <v>0.15972950135140701</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13">
+        <v>0.48170220925510099</v>
+      </c>
+      <c r="E13">
+        <v>9.1362751528122302E-2</v>
+      </c>
+      <c r="F13">
+        <v>0.442517647183027</v>
+      </c>
+      <c r="G13">
+        <v>0.18699811887828899</v>
+      </c>
+      <c r="H13">
+        <v>0.48638172712371303</v>
+      </c>
+      <c r="I13">
+        <v>0.18774211554039699</v>
+      </c>
+      <c r="J13">
+        <v>0.49533571042811497</v>
+      </c>
+      <c r="K13">
+        <v>0.27305047207241701</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14">
+        <v>0.50554308099894696</v>
+      </c>
+      <c r="E14">
+        <v>0.149437193816157</v>
+      </c>
+      <c r="F14">
+        <v>0.64977656476882695</v>
+      </c>
+      <c r="G14">
+        <v>0.13889635397580399</v>
+      </c>
+      <c r="H14">
+        <v>0.506643137228177</v>
+      </c>
+      <c r="I14">
+        <v>0.15330933742574501</v>
+      </c>
+      <c r="J14">
+        <v>0.97001826162678495</v>
+      </c>
+      <c r="K14">
+        <v>8.7328320605564599E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" t="s">
         <v>14</v>
       </c>
-      <c r="D13">
+      <c r="D15">
+        <v>0.49129482313377798</v>
+      </c>
+      <c r="E15">
+        <v>7.5358831299851894E-2</v>
+      </c>
+      <c r="F15">
+        <v>0.48393782367103999</v>
+      </c>
+      <c r="G15">
+        <v>0.121118662713112</v>
+      </c>
+      <c r="H15">
+        <v>0.503360373519258</v>
+      </c>
+      <c r="I15">
+        <v>0.16494107339281899</v>
+      </c>
+      <c r="J15">
+        <v>0.50658366714391301</v>
+      </c>
+      <c r="K15">
+        <v>0.128437923303589</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16">
+        <v>0.492532923063976</v>
+      </c>
+      <c r="E16">
+        <v>6.8868775282144898E-2</v>
+      </c>
+      <c r="F16">
+        <v>0.47788124452720798</v>
+      </c>
+      <c r="G16">
+        <v>0.13079234076138799</v>
+      </c>
+      <c r="H16">
+        <v>0.51273895300985906</v>
+      </c>
+      <c r="I16">
+        <v>0.179412442059288</v>
+      </c>
+      <c r="J16">
+        <v>0.50876684555114104</v>
+      </c>
+      <c r="K16">
+        <v>0.18044341420302301</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17">
+        <v>0.48071066233383197</v>
+      </c>
+      <c r="E17">
+        <v>9.6316347525856702E-2</v>
+      </c>
+      <c r="F17">
+        <v>0.42856905378954502</v>
+      </c>
+      <c r="G17">
+        <v>0.19728789970702901</v>
+      </c>
+      <c r="H17">
+        <v>0.47769563083615801</v>
+      </c>
+      <c r="I17">
+        <v>0.180074190093264</v>
+      </c>
+      <c r="J17">
+        <v>0.47405878979592497</v>
+      </c>
+      <c r="K17">
+        <v>0.26708632082406902</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18">
+        <v>0.51550387596899205</v>
+      </c>
+      <c r="E18">
+        <v>0.17251811765168401</v>
+      </c>
+      <c r="F18">
+        <v>0.59471665285618702</v>
+      </c>
+      <c r="G18">
+        <v>0.18753211096234301</v>
+      </c>
+      <c r="H18">
+        <v>0.49889258028792899</v>
+      </c>
+      <c r="I18">
+        <v>0.20636506381518299</v>
+      </c>
+      <c r="J18">
+        <v>0.80404208194905802</v>
+      </c>
+      <c r="K18">
+        <v>0.20711232758545101</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19">
+        <v>0.53197674418604601</v>
+      </c>
+      <c r="E19">
+        <v>0.18117650340232599</v>
+      </c>
+      <c r="F19">
+        <v>0.49334076775937202</v>
+      </c>
+      <c r="G19">
+        <v>0.178552174200312</v>
+      </c>
+      <c r="H19">
+        <v>0.55495570321151699</v>
+      </c>
+      <c r="I19">
+        <v>0.24335929593338099</v>
+      </c>
+      <c r="J19">
+        <v>0.51561461794019903</v>
+      </c>
+      <c r="K19">
+        <v>0.219269172902882</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20">
+        <v>0.53133074935400504</v>
+      </c>
+      <c r="E20">
+        <v>0.155617057772441</v>
+      </c>
+      <c r="F20">
+        <v>0.44240785054738502</v>
+      </c>
+      <c r="G20">
+        <v>0.21885537992434601</v>
+      </c>
+      <c r="H20">
+        <v>0.51589147286821702</v>
+      </c>
+      <c r="I20">
+        <v>0.29171789544013399</v>
+      </c>
+      <c r="J20">
+        <v>0.44158361018826098</v>
+      </c>
+      <c r="K20">
+        <v>0.246619473264934</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21" t="s">
+        <v>14</v>
+      </c>
+      <c r="D21">
         <v>0.48191214470284199</v>
       </c>
-      <c r="E13">
+      <c r="E21">
         <v>0.21119980804774</v>
       </c>
-      <c r="F13">
+      <c r="F21">
         <v>0.404829924597366</v>
       </c>
-      <c r="G13">
+      <c r="G21">
         <v>0.288242341868583</v>
       </c>
-      <c r="H13">
+      <c r="H21">
         <v>0.440669988925802</v>
       </c>
-      <c r="I13">
+      <c r="I21">
         <v>0.325237869278242</v>
       </c>
-      <c r="J13">
+      <c r="J21">
         <v>0.42059800664451802</v>
       </c>
-      <c r="K13">
+      <c r="K21">
         <v>0.31620061780796399</v>
       </c>
     </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C22" t="s">
+        <v>12</v>
+      </c>
+      <c r="D22">
+        <v>0.50674161242912497</v>
+      </c>
+      <c r="E22">
+        <v>0.15380639937964799</v>
+      </c>
+      <c r="F22">
+        <v>0.65347187856222799</v>
+      </c>
+      <c r="G22">
+        <v>0.14079478301534401</v>
+      </c>
+      <c r="H22">
+        <v>0.50617617192825404</v>
+      </c>
+      <c r="I22">
+        <v>0.15554310177492101</v>
+      </c>
+      <c r="J22">
+        <v>0.97941576029530397</v>
+      </c>
+      <c r="K22">
+        <v>4.2865762445541897E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C23" t="s">
+        <v>14</v>
+      </c>
+      <c r="D23">
+        <v>0.51712587527708298</v>
+      </c>
+      <c r="E23">
+        <v>4.6991288412863402E-2</v>
+      </c>
+      <c r="F23">
+        <v>0.50329899393506905</v>
+      </c>
+      <c r="G23">
+        <v>9.1894101185035507E-2</v>
+      </c>
+      <c r="H23">
+        <v>0.52648682759423804</v>
+      </c>
+      <c r="I23">
+        <v>0.158543303223005</v>
+      </c>
+      <c r="J23">
+        <v>0.51440451495236905</v>
+      </c>
+      <c r="K23">
+        <v>8.7907563856916102E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C24" t="s">
+        <v>13</v>
+      </c>
+      <c r="D24">
+        <v>0.50511695483430996</v>
+      </c>
+      <c r="E24">
+        <v>9.9481054875894398E-2</v>
+      </c>
+      <c r="F24">
+        <v>0.49316496933821302</v>
+      </c>
+      <c r="G24">
+        <v>0.16571902851701201</v>
+      </c>
+      <c r="H24">
+        <v>0.50696363972189695</v>
+      </c>
+      <c r="I24">
+        <v>0.17293266377453201</v>
+      </c>
+      <c r="J24">
+        <v>0.54520776996638798</v>
+      </c>
+      <c r="K24">
+        <v>0.22612454444108299</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25" t="s">
+        <v>11</v>
+      </c>
+      <c r="D25">
+        <v>0.50545708678685097</v>
+      </c>
+      <c r="E25">
+        <v>8.10938019695919E-2</v>
+      </c>
+      <c r="F25">
+        <v>0.47635869070235798</v>
+      </c>
+      <c r="G25">
+        <v>0.11746894334435699</v>
+      </c>
+      <c r="H25">
+        <v>0.51719997660110495</v>
+      </c>
+      <c r="I25">
+        <v>0.16539222280739799</v>
+      </c>
+      <c r="J25">
+        <v>0.48597775861242198</v>
+      </c>
+      <c r="K25">
+        <v>0.154065738941457</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K17" xr:uid="{20B60A1F-9449-4A91-8C37-2E569624DE33}"/>
+  <autoFilter ref="A1:K25" xr:uid="{20B60A1F-9449-4A91-8C37-2E569624DE33}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{926F4F26-DE01-4BB2-9AB3-84FA32AC1323}">
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.88671875" customWidth="1"/>
@@ -1246,337 +1681,643 @@
         <v>15</v>
       </c>
       <c r="H1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1" t="s">
         <v>18</v>
       </c>
-      <c r="I1" t="s">
+      <c r="M1" t="s">
         <v>18</v>
       </c>
-      <c r="J1" t="s">
+      <c r="N1" t="s">
         <v>18</v>
       </c>
-      <c r="K1" t="s">
+      <c r="O1" t="s">
         <v>18</v>
       </c>
-      <c r="L1" t="s">
-        <v>17</v>
-      </c>
-      <c r="M1" t="s">
-        <v>17</v>
-      </c>
-      <c r="N1" t="s">
-        <v>17</v>
-      </c>
-      <c r="O1" t="s">
-        <v>17</v>
-      </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="29"/>
+      <c r="L2" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="M2" s="28"/>
+      <c r="N2" s="28"/>
+      <c r="O2" s="29"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B3" s="32"/>
+      <c r="C3" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="I2" s="27"/>
-      <c r="J2" s="27"/>
-      <c r="K2" s="28"/>
-      <c r="L2" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="M2" s="27"/>
-      <c r="N2" s="27"/>
-      <c r="O2" s="28"/>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B3" s="31"/>
-      <c r="C3" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" s="4" t="s">
+      <c r="H3" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="I3" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="J3" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="H3" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3" s="4" t="s">
+      <c r="K3" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="M3" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="K3" s="9" t="s">
+      <c r="N3" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="L3" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="O3" s="9" t="s">
-        <v>23</v>
+      <c r="O3" s="10" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="29" t="s">
-        <v>29</v>
+        <v>17</v>
+      </c>
+      <c r="B4" s="30" t="s">
+        <v>30</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="12" t="str">
+      <c r="D4" s="13" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C4,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A4)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C4,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A4)*100,2),"0.00")</f>
-        <v>51.2274 ± 16.34</v>
-      </c>
-      <c r="E4" s="6" t="str">
+        <v>49.2533 ± 6.89</v>
+      </c>
+      <c r="E4" s="7" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C4,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A4)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C4,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A4)*100,2),"0.00")</f>
-        <v>43.7214 ± 21.69</v>
+        <v>47.7881 ± 13.08</v>
       </c>
       <c r="F4" s="6" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C4,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A4)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C4,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A4)*100,2),"0.00")</f>
-        <v>48.4275 ± 28.96</v>
-      </c>
-      <c r="G4" s="13" t="str">
+        <v>51.2739 ± 17.94</v>
+      </c>
+      <c r="G4" s="14" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C4,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A4)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C4,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A4)*100,2),"0.00")</f>
-        <v>46.7885 ± 26.80</v>
-      </c>
-      <c r="H4" s="17" t="str">
+        <v>50.8767 ± 18.04</v>
+      </c>
+      <c r="H4" s="13" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C4,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A4)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C4,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A4)*100,2),"0.00")</f>
-        <v>53.1977 ± 18.12</v>
-      </c>
-      <c r="I4" s="6" t="str">
+        <v>50.5457 ± 8.11</v>
+      </c>
+      <c r="I4" s="7" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C4,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A4)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C4,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A4)*100,2),"0.00")</f>
-        <v>49.3341 ± 17.86</v>
-      </c>
-      <c r="J4" s="5" t="str">
+        <v>47.6359 ± 11.75</v>
+      </c>
+      <c r="J4" s="7" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C4,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A4)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C4,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A4)*100,2),"0.00")</f>
-        <v>55.4956 ± 24.34</v>
-      </c>
-      <c r="K4" s="13" t="str">
+        <v>51.7200 ± 16.54</v>
+      </c>
+      <c r="K4" s="14" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C4,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A4)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C4,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A4)*100,2),"0.00")</f>
-        <v>51.5615 ± 21.93</v>
-      </c>
-      <c r="L4" s="12" t="str">
+        <v>48.5978 ± 15.41</v>
+      </c>
+      <c r="L4" s="13" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C4,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A4)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C4,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A4)*100,2),"0.00")</f>
-        <v>44.8643 ± 18.45</v>
-      </c>
-      <c r="M4" s="6" t="str">
+        <v>48.6513 ± 6.13</v>
+      </c>
+      <c r="M4" s="7" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C4,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A4)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C4,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A4)*100,2),"0.00")</f>
-        <v>36.6928 ± 23.35</v>
-      </c>
-      <c r="N4" s="6" t="str">
+        <v>45.7562 ± 11.07</v>
+      </c>
+      <c r="N4" s="7" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C4,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A4)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C4,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A4)*100,2),"0.00")</f>
-        <v>38.4330 ± 27.20</v>
-      </c>
-      <c r="O4" s="13" t="str">
+        <v>49.9124 ± 15.87</v>
+      </c>
+      <c r="O4" s="14" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C4,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A4)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C4,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A4)*100,2),"0.00")</f>
-        <v>39.6401 ± 27.90</v>
+        <v>47.1086 ± 15.97</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="29"/>
-      <c r="C5" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="30"/>
+      <c r="C5" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="32" t="str">
+      <c r="D5" s="11" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C5,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A5)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C5,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A5)*100,2),"0.00")</f>
-        <v>56.5245 ± 15.78</v>
-      </c>
-      <c r="E5" s="7" t="str">
+        <v>48.0711 ± 9.63</v>
+      </c>
+      <c r="E5" s="8" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C5,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A5)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C5,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A5)*100,2),"0.00")</f>
-        <v>51.8379 ± 21.90</v>
-      </c>
-      <c r="F5" s="7" t="str">
+        <v>42.8569 ± 19.73</v>
+      </c>
+      <c r="F5" s="8" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C5,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A5)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C5,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A5)*100,2),"0.00")</f>
-        <v>52.4751 ± 23.18</v>
-      </c>
-      <c r="G5" s="11" t="str">
+        <v>47.7696 ± 18.01</v>
+      </c>
+      <c r="G5" s="12" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C5,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A5)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C5,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A5)*100,2),"0.00")</f>
-        <v>58.9037 ± 30.89</v>
-      </c>
-      <c r="H5" s="10" t="str">
+        <v>47.4059 ± 26.71</v>
+      </c>
+      <c r="H5" s="11" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C5,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A5)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C5,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A5)*100,2),"0.00")</f>
-        <v>53.1331 ± 15.56</v>
-      </c>
-      <c r="I5" s="7" t="str">
+        <v>50.5117 ± 9.95</v>
+      </c>
+      <c r="I5" s="8" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C5,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A5)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C5,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A5)*100,2),"0.00")</f>
-        <v>44.2408 ± 21.89</v>
-      </c>
-      <c r="J5" s="7" t="str">
+        <v>49.3165 ± 16.57</v>
+      </c>
+      <c r="J5" s="8" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C5,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A5)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C5,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A5)*100,2),"0.00")</f>
-        <v>51.5891 ± 29.17</v>
-      </c>
-      <c r="K5" s="11" t="str">
+        <v>50.6964 ± 17.29</v>
+      </c>
+      <c r="K5" s="12" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C5,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A5)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C5,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A5)*100,2),"0.00")</f>
-        <v>44.1584 ± 24.66</v>
-      </c>
-      <c r="L5" s="10" t="str">
+        <v>54.5208 ± 22.61</v>
+      </c>
+      <c r="L5" s="11" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C5,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A5)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C5,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A5)*100,2),"0.00")</f>
-        <v>52.1318 ± 17.44</v>
-      </c>
-      <c r="M5" s="7" t="str">
+        <v>48.1702 ± 9.14</v>
+      </c>
+      <c r="M5" s="8" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C5,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A5)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C5,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A5)*100,2),"0.00")</f>
-        <v>43.4565 ± 24.29</v>
-      </c>
-      <c r="N5" s="7" t="str">
+        <v>44.2518 ± 18.70</v>
+      </c>
+      <c r="N5" s="8" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C5,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A5)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C5,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A5)*100,2),"0.00")</f>
-        <v>46.4849 ± 29.32</v>
-      </c>
-      <c r="O5" s="11" t="str">
+        <v>48.6382 ± 18.77</v>
+      </c>
+      <c r="O5" s="12" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C5,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A5)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C5,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A5)*100,2),"0.00")</f>
-        <v>48.0122 ± 30.60</v>
+        <v>49.5336 ± 27.31</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="29"/>
+        <v>17</v>
+      </c>
+      <c r="B6" s="30"/>
       <c r="C6" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="12" t="str">
+      <c r="D6" s="18" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C6,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A6)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C6,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A6)*100,2),"0.00")</f>
-        <v>55.7494 ± 15.35</v>
-      </c>
-      <c r="E6" s="5" t="str">
+        <v>50.5543 ± 14.94</v>
+      </c>
+      <c r="E6" s="6" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C6,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A6)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C6,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A6)*100,2),"0.00")</f>
-        <v>63.3120 ± 15.38</v>
-      </c>
-      <c r="F6" s="5" t="str">
+        <v>64.9777 ± 13.89</v>
+      </c>
+      <c r="F6" s="7" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C6,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A6)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C6,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A6)*100,2),"0.00")</f>
-        <v>52.4908 ± 16.67</v>
-      </c>
-      <c r="G6" s="18" t="str">
+        <v>50.6643 ± 15.33</v>
+      </c>
+      <c r="G6" s="19" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C6,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A6)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C6,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A6)*100,2),"0.00")</f>
-        <v>86.0576 ± 17.68</v>
-      </c>
-      <c r="H6" s="12" t="str">
+        <v>97.0018 ± 8.73</v>
+      </c>
+      <c r="H6" s="13" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C6,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A6)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C6,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A6)*100,2),"0.00")</f>
-        <v>51.5504 ± 17.25</v>
-      </c>
-      <c r="I6" s="5" t="str">
+        <v>50.6742 ± 15.38</v>
+      </c>
+      <c r="I6" s="6" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C6,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A6)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C6,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A6)*100,2),"0.00")</f>
-        <v>59.4717 ± 18.75</v>
-      </c>
-      <c r="J6" s="6" t="str">
+        <v>65.3472 ± 14.08</v>
+      </c>
+      <c r="J6" s="7" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C6,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A6)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C6,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A6)*100,2),"0.00")</f>
-        <v>49.8893 ± 20.64</v>
-      </c>
-      <c r="K6" s="18" t="str">
+        <v>50.6176 ± 15.55</v>
+      </c>
+      <c r="K6" s="19" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C6,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A6)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C6,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A6)*100,2),"0.00")</f>
-        <v>80.4042 ± 20.71</v>
-      </c>
-      <c r="L6" s="17" t="str">
+        <v>97.9416 ± 4.29</v>
+      </c>
+      <c r="L6" s="18" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C6,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A6)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C6,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A6)*100,2),"0.00")</f>
-        <v>56.0078 ± 16.34</v>
-      </c>
-      <c r="M6" s="5" t="str">
+        <v>50.4261 ± 15.13</v>
+      </c>
+      <c r="M6" s="6" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C6,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A6)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C6,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A6)*100,2),"0.00")</f>
-        <v>62.2730 ± 18.71</v>
-      </c>
-      <c r="N6" s="5" t="str">
+        <v>64.8184 ± 14.03</v>
+      </c>
+      <c r="N6" s="6" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C6,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A6)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C6,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A6)*100,2),"0.00")</f>
-        <v>52.2490 ± 18.39</v>
-      </c>
-      <c r="O6" s="18" t="str">
+        <v>50.5304 ± 15.42</v>
+      </c>
+      <c r="O6" s="19" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C6,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A6)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C6,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A6)*100,2),"0.00")</f>
-        <v>83.1894 ± 24.74</v>
+        <v>96.5472 ± 8.17</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="31"/>
+      <c r="C7" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="15" t="str">
+        <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C7,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A7)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C7,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A7)*100,2),"0.00")</f>
+        <v>49.1295 ± 7.54</v>
+      </c>
+      <c r="E7" s="16" t="str">
+        <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C7,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A7)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C7,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A7)*100,2),"0.00")</f>
+        <v>48.3938 ± 12.11</v>
+      </c>
+      <c r="F7" s="16" t="str">
+        <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C7,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A7)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C7,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A7)*100,2),"0.00")</f>
+        <v>50.3360 ± 16.49</v>
+      </c>
+      <c r="G7" s="17" t="str">
+        <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C7,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A7)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C7,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A7)*100,2),"0.00")</f>
+        <v>50.6584 ± 12.84</v>
+      </c>
+      <c r="H7" s="33" t="str">
+        <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C7,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A7)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C7,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A7)*100,2),"0.00")</f>
+        <v>51.7126 ± 4.70</v>
+      </c>
+      <c r="I7" s="16" t="str">
+        <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C7,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A7)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C7,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A7)*100,2),"0.00")</f>
+        <v>50.3299 ± 9.19</v>
+      </c>
+      <c r="J7" s="34" t="str">
+        <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C7,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A7)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C7,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A7)*100,2),"0.00")</f>
+        <v>52.6487 ± 15.85</v>
+      </c>
+      <c r="K7" s="17" t="str">
+        <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C7,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A7)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C7,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A7)*100,2),"0.00")</f>
+        <v>51.4405 ± 8.79</v>
+      </c>
+      <c r="L7" s="15" t="str">
+        <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C7,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A7)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C7,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A7)*100,2),"0.00")</f>
+        <v>48.8131 ± 5.02</v>
+      </c>
+      <c r="M7" s="16" t="str">
+        <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C7,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A7)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C7,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A7)*100,2),"0.00")</f>
+        <v>47.1680 ± 11.00</v>
+      </c>
+      <c r="N7" s="16" t="str">
+        <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C7,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A7)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C7,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A7)*100,2),"0.00")</f>
+        <v>49.6984 ± 16.82</v>
+      </c>
+      <c r="O7" s="17" t="str">
+        <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C7,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A7)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C7,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A7)*100,2),"0.00")</f>
+        <v>48.1285 ± 10.56</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="1"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B9" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="25"/>
+      <c r="F9" s="25"/>
+      <c r="G9" s="26"/>
+      <c r="H9" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
+      <c r="K9" s="29"/>
+      <c r="L9" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="M9" s="28"/>
+      <c r="N9" s="28"/>
+      <c r="O9" s="29"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B10" s="32"/>
+      <c r="C10" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="K10" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="M10" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="N10" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="O10" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="30"/>
-      <c r="C7" s="20" t="s">
+      <c r="B11" s="30" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="13" t="str">
+        <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C11,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A11)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C11,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A11)*100,2),"0.00")</f>
+        <v>51.2274 ± 16.34</v>
+      </c>
+      <c r="E11" s="7" t="str">
+        <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C11,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A11)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C11,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A11)*100,2),"0.00")</f>
+        <v>43.7214 ± 21.69</v>
+      </c>
+      <c r="F11" s="7" t="str">
+        <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C11,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A11)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C11,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A11)*100,2),"0.00")</f>
+        <v>48.4275 ± 28.96</v>
+      </c>
+      <c r="G11" s="14" t="str">
+        <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C11,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A11)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C11,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A11)*100,2),"0.00")</f>
+        <v>46.7885 ± 26.80</v>
+      </c>
+      <c r="H11" s="13" t="str">
+        <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C11,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A11)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C11,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A11)*100,2),"0.00")</f>
+        <v>53.1977 ± 18.12</v>
+      </c>
+      <c r="I11" s="7" t="str">
+        <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C11,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A11)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C11,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A11)*100,2),"0.00")</f>
+        <v>49.3341 ± 17.86</v>
+      </c>
+      <c r="J11" s="6" t="str">
+        <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C11,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A11)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C11,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A11)*100,2),"0.00")</f>
+        <v>55.4956 ± 24.34</v>
+      </c>
+      <c r="K11" s="14" t="str">
+        <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C11,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A11)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C11,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A11)*100,2),"0.00")</f>
+        <v>51.5615 ± 21.93</v>
+      </c>
+      <c r="L11" s="13" t="str">
+        <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C11,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A11)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C11,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A11)*100,2),"0.00")</f>
+        <v>44.8643 ± 18.45</v>
+      </c>
+      <c r="M11" s="7" t="str">
+        <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C11,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A11)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C11,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A11)*100,2),"0.00")</f>
+        <v>36.6928 ± 23.35</v>
+      </c>
+      <c r="N11" s="7" t="str">
+        <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C11,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A11)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C11,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A11)*100,2),"0.00")</f>
+        <v>38.4330 ± 27.20</v>
+      </c>
+      <c r="O11" s="14" t="str">
+        <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C11,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A11)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C11,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A11)*100,2),"0.00")</f>
+        <v>39.6401 ± 27.90</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="30"/>
+      <c r="C12" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="35" t="str">
+        <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C12,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A12)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C12,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A12)*100,2),"0.00")</f>
+        <v>56.5245 ± 15.78</v>
+      </c>
+      <c r="E12" s="8" t="str">
+        <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C12,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A12)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C12,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A12)*100,2),"0.00")</f>
+        <v>51.8379 ± 21.90</v>
+      </c>
+      <c r="F12" s="8" t="str">
+        <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C12,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A12)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C12,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A12)*100,2),"0.00")</f>
+        <v>52.4751 ± 23.18</v>
+      </c>
+      <c r="G12" s="12" t="str">
+        <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C12,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A12)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C12,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A12)*100,2),"0.00")</f>
+        <v>58.9037 ± 30.89</v>
+      </c>
+      <c r="H12" s="35" t="str">
+        <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C12,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A12)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C12,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A12)*100,2),"0.00")</f>
+        <v>53.1331 ± 15.56</v>
+      </c>
+      <c r="I12" s="8" t="str">
+        <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C12,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A12)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C12,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A12)*100,2),"0.00")</f>
+        <v>44.2408 ± 21.89</v>
+      </c>
+      <c r="J12" s="8" t="str">
+        <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C12,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A12)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C12,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A12)*100,2),"0.00")</f>
+        <v>51.5891 ± 29.17</v>
+      </c>
+      <c r="K12" s="12" t="str">
+        <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C12,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A12)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C12,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A12)*100,2),"0.00")</f>
+        <v>44.1584 ± 24.66</v>
+      </c>
+      <c r="L12" s="11" t="str">
+        <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C12,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A12)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C12,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A12)*100,2),"0.00")</f>
+        <v>52.1318 ± 17.44</v>
+      </c>
+      <c r="M12" s="8" t="str">
+        <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C12,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A12)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C12,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A12)*100,2),"0.00")</f>
+        <v>43.4565 ± 24.29</v>
+      </c>
+      <c r="N12" s="8" t="str">
+        <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C12,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A12)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C12,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A12)*100,2),"0.00")</f>
+        <v>46.4849 ± 29.32</v>
+      </c>
+      <c r="O12" s="12" t="str">
+        <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C12,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A12)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C12,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A12)*100,2),"0.00")</f>
+        <v>48.0122 ± 30.60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="30"/>
+      <c r="C13" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="13" t="str">
+        <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C13,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A13)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C13,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A13)*100,2),"0.00")</f>
+        <v>55.7494 ± 15.35</v>
+      </c>
+      <c r="E13" s="6" t="str">
+        <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C13,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A13)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C13,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A13)*100,2),"0.00")</f>
+        <v>63.3120 ± 15.38</v>
+      </c>
+      <c r="F13" s="6" t="str">
+        <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C13,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A13)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C13,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A13)*100,2),"0.00")</f>
+        <v>52.4908 ± 16.67</v>
+      </c>
+      <c r="G13" s="19" t="str">
+        <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C13,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A13)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C13,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A13)*100,2),"0.00")</f>
+        <v>86.0576 ± 17.68</v>
+      </c>
+      <c r="H13" s="13" t="str">
+        <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C13,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A13)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C13,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A13)*100,2),"0.00")</f>
+        <v>51.5504 ± 17.25</v>
+      </c>
+      <c r="I13" s="6" t="str">
+        <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C13,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A13)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C13,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A13)*100,2),"0.00")</f>
+        <v>59.4717 ± 18.75</v>
+      </c>
+      <c r="J13" s="7" t="str">
+        <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C13,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A13)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C13,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A13)*100,2),"0.00")</f>
+        <v>49.8893 ± 20.64</v>
+      </c>
+      <c r="K13" s="19" t="str">
+        <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C13,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A13)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C13,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A13)*100,2),"0.00")</f>
+        <v>80.4042 ± 20.71</v>
+      </c>
+      <c r="L13" s="18" t="str">
+        <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C13,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A13)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C13,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A13)*100,2),"0.00")</f>
+        <v>56.0078 ± 16.34</v>
+      </c>
+      <c r="M13" s="6" t="str">
+        <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C13,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A13)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C13,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A13)*100,2),"0.00")</f>
+        <v>62.2730 ± 18.71</v>
+      </c>
+      <c r="N13" s="6" t="str">
+        <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C13,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A13)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C13,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A13)*100,2),"0.00")</f>
+        <v>52.2490 ± 18.39</v>
+      </c>
+      <c r="O13" s="19" t="str">
+        <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C13,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A13)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C13,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A13)*100,2),"0.00")</f>
+        <v>83.1894 ± 24.74</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="31"/>
+      <c r="C14" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="14" t="str">
-        <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C7,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A7)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C7,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A7)*100,2),"0.00")</f>
+      <c r="D14" s="15" t="str">
+        <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C14,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A14)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C14,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A14)*100,2),"0.00")</f>
         <v>44.5736 ± 14.40</v>
       </c>
-      <c r="E7" s="15" t="str">
-        <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C7,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A7)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C7,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A7)*100,2),"0.00")</f>
+      <c r="E14" s="16" t="str">
+        <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C14,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A14)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C14,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A14)*100,2),"0.00")</f>
         <v>45.7373 ± 17.67</v>
       </c>
-      <c r="F7" s="15" t="str">
-        <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C7,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A7)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C7,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A7)*100,2),"0.00")</f>
+      <c r="F14" s="16" t="str">
+        <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C14,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A14)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C14,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A14)*100,2),"0.00")</f>
         <v>41.9260 ± 16.99</v>
       </c>
-      <c r="G7" s="16" t="str">
-        <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C7,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A7)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C7,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A7)*100,2),"0.00")</f>
+      <c r="G14" s="17" t="str">
+        <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C14,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A14)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C14,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A14)*100,2),"0.00")</f>
         <v>56.5891 ± 26.11</v>
       </c>
-      <c r="H7" s="14" t="str">
-        <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C7,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A7)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C7,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A7)*100,2),"0.00")</f>
+      <c r="H14" s="15" t="str">
+        <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C14,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A14)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C14,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A14)*100,2),"0.00")</f>
         <v>48.1912 ± 21.12</v>
       </c>
-      <c r="I7" s="15" t="str">
-        <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C7,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A7)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C7,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A7)*100,2),"0.00")</f>
+      <c r="I14" s="16" t="str">
+        <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C14,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A14)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C14,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A14)*100,2),"0.00")</f>
         <v>40.4830 ± 28.82</v>
       </c>
-      <c r="J7" s="15" t="str">
-        <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C7,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A7)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C7,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A7)*100,2),"0.00")</f>
+      <c r="J14" s="16" t="str">
+        <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C14,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A14)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C14,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A14)*100,2),"0.00")</f>
         <v>44.0670 ± 32.52</v>
       </c>
-      <c r="K7" s="16" t="str">
-        <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C7,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A7)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C7,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A7)*100,2),"0.00")</f>
+      <c r="K14" s="17" t="str">
+        <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C14,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A14)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C14,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A14)*100,2),"0.00")</f>
         <v>42.0598 ± 31.62</v>
       </c>
-      <c r="L7" s="14" t="str">
-        <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C7,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A7)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C7,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A7)*100,2),"0.00")</f>
+      <c r="L14" s="15" t="str">
+        <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C14,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A14)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C14,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A14)*100,2),"0.00")</f>
         <v>46.0917 ± 18.75</v>
       </c>
-      <c r="M7" s="15" t="str">
-        <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C7,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A7)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C7,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A7)*100,2),"0.00")</f>
+      <c r="M14" s="16" t="str">
+        <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C14,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A14)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C14,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A14)*100,2),"0.00")</f>
         <v>43.1921 ± 21.29</v>
       </c>
-      <c r="N7" s="15" t="str">
-        <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C7,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A7)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C7,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A7)*100,2),"0.00")</f>
+      <c r="N14" s="16" t="str">
+        <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C14,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A14)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C14,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A14)*100,2),"0.00")</f>
         <v>43.1700 ± 23.66</v>
       </c>
-      <c r="O7" s="16" t="str">
-        <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C7,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A7)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C7,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A7)*100,2),"0.00")</f>
+      <c r="O14" s="17" t="str">
+        <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C14,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A14)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C14,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A14)*100,2),"0.00")</f>
         <v>48.9646 ± 25.91</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="B4:B7"/>
-    <mergeCell ref="B2:B3"/>
+  <mergeCells count="10">
     <mergeCell ref="D2:G2"/>
     <mergeCell ref="H2:K2"/>
     <mergeCell ref="L2:O2"/>
+    <mergeCell ref="B4:B7"/>
+    <mergeCell ref="B11:B14"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="D9:G9"/>
+    <mergeCell ref="H9:K9"/>
+    <mergeCell ref="L9:O9"/>
   </mergeCells>
-  <conditionalFormatting sqref="D4:G7">
+  <conditionalFormatting sqref="D4:O7 D11:G14">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -1588,7 +2329,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H4:K7">
+  <conditionalFormatting sqref="H11:K14">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -1600,7 +2341,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L4:O7">
+  <conditionalFormatting sqref="L11:O14">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
